--- a/공사 데이터 입력 자동화/6월_매출손익현황.xlsx
+++ b/공사 데이터 입력 자동화/6월_매출손익현황.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\조성현\Documents\GitHub\yjs_Dashboard\공사 데이터 입력 자동화\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0419091C-68BB-4590-8BDC-9718A988EF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074004F3-0B22-4668-B794-2E62D3B70ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4710" yWindow="375" windowWidth="22620" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-900" yWindow="1065" windowWidth="22620" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6월 공정현황" sheetId="2" r:id="rId1"/>
     <sheet name="6월 8일" sheetId="3" r:id="rId2"/>
     <sheet name="6월 9일" sheetId="4" r:id="rId3"/>
+    <sheet name="6월 10일" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="299">
   <si>
     <t>JY25-256</t>
   </si>
@@ -3149,6 +3150,9 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="21" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3157,9 +3161,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3528,22 +3529,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41"/>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
+      <c r="A1" s="42"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="3" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3600,11 +3601,11 @@
         <v>30000000</v>
       </c>
       <c r="E5" s="2">
-        <v>22881116</v>
+        <v>26114317.32</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" si="0"/>
-        <v>0.76270386666666667</v>
+        <v>0.87047724400000004</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -4156,22 +4157,22 @@
       </c>
       <c r="E32" s="6">
         <f>SUM(E4:E31)</f>
-        <v>51495703.079999998</v>
+        <v>54728904.399999999</v>
       </c>
       <c r="F32" s="7">
         <f>IF(D32&gt;0,E32/D32,"-")</f>
-        <v>0.11996669325567851</v>
+        <v>0.12749890366919045</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="43" t="s">
+      <c r="A34" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
     </row>
     <row r="35" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -4326,11 +4327,11 @@
       </c>
       <c r="E48" s="12">
         <f>E32+E46</f>
-        <v>59133935.079999998</v>
+        <v>62367136.399999999</v>
       </c>
       <c r="F48" s="13">
         <f>E48/D48</f>
-        <v>0.13776106017472334</v>
+        <v>0.1452932705882353</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
@@ -6785,7 +6786,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="41" t="s">
         <v>83</v>
       </c>
       <c r="B1" s="24" t="s">
@@ -9201,6 +9202,2446 @@
       </c>
       <c r="C345" s="39">
         <v>54035424.840000004</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="40"/>
+      <c r="B346" s="40"/>
+      <c r="C346" s="40"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE5DBBE-FC44-4248-8D66-BE79894FA05F}">
+  <dimension ref="A1:C346"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+    </row>
+    <row r="3" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+    </row>
+    <row r="6" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+    </row>
+    <row r="9" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+    </row>
+    <row r="15" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="28">
+        <v>203500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="35"/>
+      <c r="C18" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+    </row>
+    <row r="21" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+    </row>
+    <row r="24" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="34"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+    </row>
+    <row r="27" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+    </row>
+    <row r="30" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="34"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+    </row>
+    <row r="36" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="25"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+    </row>
+    <row r="39" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+    </row>
+    <row r="42" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="34"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="25"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+    </row>
+    <row r="45" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+    </row>
+    <row r="48" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="34"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="25"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+    </row>
+    <row r="51" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+    </row>
+    <row r="54" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="34"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="25"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25"/>
+    </row>
+    <row r="57" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C57" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="29"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+    </row>
+    <row r="60" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B60" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="C60" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="34"/>
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="25"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+    </row>
+    <row r="63" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="29"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="B66" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C66" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="34"/>
+      <c r="B67" s="34"/>
+      <c r="C67" s="34"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="25"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+    </row>
+    <row r="69" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="29"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
+    </row>
+    <row r="72" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="B72" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="C72" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="34"/>
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="25"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+    </row>
+    <row r="75" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C75" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="29"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="30"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="30"/>
+    </row>
+    <row r="78" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="C78" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="34"/>
+      <c r="B79" s="34"/>
+      <c r="C79" s="34"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="25"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+    </row>
+    <row r="81" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C81" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="29"/>
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="30"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
+    </row>
+    <row r="84" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C84" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="34"/>
+      <c r="B85" s="34"/>
+      <c r="C85" s="34"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="25"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+    </row>
+    <row r="87" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A87" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C87" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="29"/>
+      <c r="B88" s="29"/>
+      <c r="C88" s="29"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="30"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
+    </row>
+    <row r="90" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B90" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C90" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="34"/>
+      <c r="B91" s="34"/>
+      <c r="C91" s="34"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="25"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="25"/>
+    </row>
+    <row r="93" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A93" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B93" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C93" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="29"/>
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="30"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
+    </row>
+    <row r="96" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B96" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C96" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="34"/>
+      <c r="B97" s="34"/>
+      <c r="C97" s="34"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="25"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="25"/>
+    </row>
+    <row r="99" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A99" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B99" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="C99" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="29"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="29"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="30"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="30"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="B102" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C102" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="34"/>
+      <c r="B103" s="34"/>
+      <c r="C103" s="34"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="25"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="25"/>
+    </row>
+    <row r="105" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A105" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B105" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C105" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="29"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="29"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="30"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="30"/>
+    </row>
+    <row r="108" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A108" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B108" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="C108" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="34"/>
+      <c r="B109" s="34"/>
+      <c r="C109" s="34"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="25"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="25"/>
+    </row>
+    <row r="111" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A111" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B111" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C111" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="29"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="29"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="30"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="30"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="B114" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="C114" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="34"/>
+      <c r="B115" s="34"/>
+      <c r="C115" s="34"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="25"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="25"/>
+    </row>
+    <row r="117" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A117" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C117" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="29"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="29"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="30"/>
+    </row>
+    <row r="120" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A120" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B120" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C120" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="34"/>
+      <c r="B121" s="34"/>
+      <c r="C121" s="34"/>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="25"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="25"/>
+    </row>
+    <row r="123" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A123" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="B123" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="C123" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="29"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="29"/>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="30"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="30"/>
+    </row>
+    <row r="126" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A126" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B126" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="C126" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="34"/>
+      <c r="B127" s="34"/>
+      <c r="C127" s="34"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="25"/>
+      <c r="B128" s="25"/>
+      <c r="C128" s="25"/>
+    </row>
+    <row r="129" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="B129" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C129" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="29"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="29"/>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="30"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="30"/>
+    </row>
+    <row r="132" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A132" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="B132" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="C132" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="34"/>
+      <c r="B133" s="34"/>
+      <c r="C133" s="34"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="25"/>
+      <c r="B134" s="25"/>
+      <c r="C134" s="25"/>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="B135" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="C135" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="29"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="29"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="30"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="30"/>
+    </row>
+    <row r="138" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A138" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="B138" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C138" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="34"/>
+      <c r="B139" s="34"/>
+      <c r="C139" s="34"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="25"/>
+      <c r="B140" s="25"/>
+      <c r="C140" s="25"/>
+    </row>
+    <row r="141" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A141" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="B141" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="C141" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="29"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="29"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="30"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="30"/>
+    </row>
+    <row r="144" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A144" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B144" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C144" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="34"/>
+      <c r="B145" s="34"/>
+      <c r="C145" s="34"/>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="25"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="25"/>
+    </row>
+    <row r="147" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A147" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="B147" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C147" s="28">
+        <v>898035.92</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="29"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="29"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="30"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="30"/>
+    </row>
+    <row r="150" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A150" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B150" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="C150" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="34"/>
+      <c r="B151" s="34"/>
+      <c r="C151" s="34"/>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="25"/>
+      <c r="B152" s="25"/>
+      <c r="C152" s="25"/>
+    </row>
+    <row r="153" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A153" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="B153" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C153" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="29"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="29"/>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="30"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="30"/>
+    </row>
+    <row r="156" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A156" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="B156" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C156" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="34"/>
+      <c r="B157" s="34"/>
+      <c r="C157" s="34"/>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="25"/>
+      <c r="B158" s="25"/>
+      <c r="C158" s="25"/>
+    </row>
+    <row r="159" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A159" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="B159" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="C159" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="29"/>
+      <c r="B160" s="29"/>
+      <c r="C160" s="29"/>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="30"/>
+      <c r="B161" s="30"/>
+      <c r="C161" s="30"/>
+    </row>
+    <row r="162" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A162" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="B162" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="C162" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="34"/>
+      <c r="B163" s="34"/>
+      <c r="C163" s="34"/>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="25"/>
+      <c r="B164" s="25"/>
+      <c r="C164" s="25"/>
+    </row>
+    <row r="165" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A165" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="B165" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="C165" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="29"/>
+      <c r="B166" s="29"/>
+      <c r="C166" s="29"/>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="30"/>
+      <c r="B167" s="30"/>
+      <c r="C167" s="30"/>
+    </row>
+    <row r="168" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A168" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="B168" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="C168" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="34"/>
+      <c r="B169" s="34"/>
+      <c r="C169" s="34"/>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="25"/>
+      <c r="B170" s="25"/>
+      <c r="C170" s="25"/>
+    </row>
+    <row r="171" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A171" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="B171" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C171" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="29"/>
+      <c r="B172" s="29"/>
+      <c r="C172" s="29"/>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="30"/>
+      <c r="B173" s="30"/>
+      <c r="C173" s="30"/>
+    </row>
+    <row r="174" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A174" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="B174" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C174" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="34"/>
+      <c r="B175" s="34"/>
+      <c r="C175" s="34"/>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="25"/>
+      <c r="B176" s="25"/>
+      <c r="C176" s="25"/>
+    </row>
+    <row r="177" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A177" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="B177" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C177" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
+      <c r="C178" s="29"/>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="30"/>
+      <c r="B179" s="30"/>
+      <c r="C179" s="30"/>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="B180" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C180" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="34"/>
+      <c r="B181" s="34"/>
+      <c r="C181" s="34"/>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="25"/>
+      <c r="B182" s="25"/>
+      <c r="C182" s="25"/>
+    </row>
+    <row r="183" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A183" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="B183" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C183" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="29"/>
+      <c r="B184" s="29"/>
+      <c r="C184" s="29"/>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="30"/>
+      <c r="B185" s="30"/>
+      <c r="C185" s="30"/>
+    </row>
+    <row r="186" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A186" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="B186" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="C186" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="34"/>
+      <c r="B187" s="34"/>
+      <c r="C187" s="34"/>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="25"/>
+      <c r="B188" s="25"/>
+      <c r="C188" s="25"/>
+    </row>
+    <row r="189" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A189" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="B189" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="C189" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="29"/>
+      <c r="B190" s="29"/>
+      <c r="C190" s="29"/>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="30"/>
+      <c r="B191" s="30"/>
+      <c r="C191" s="30"/>
+    </row>
+    <row r="192" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A192" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="B192" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C192" s="33">
+        <v>405701.07</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="34"/>
+      <c r="B193" s="34"/>
+      <c r="C193" s="34"/>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="25"/>
+      <c r="B194" s="25"/>
+      <c r="C194" s="25"/>
+    </row>
+    <row r="195" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A195" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="B195" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C195" s="28">
+        <v>9903715.0800000001</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="29"/>
+      <c r="B196" s="29"/>
+      <c r="C196" s="29"/>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="30"/>
+      <c r="B197" s="30"/>
+      <c r="C197" s="30"/>
+    </row>
+    <row r="198" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A198" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B198" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="C198" s="33">
+        <v>1629647.99</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="34"/>
+      <c r="B199" s="34"/>
+      <c r="C199" s="34"/>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="25"/>
+      <c r="B200" s="25"/>
+      <c r="C200" s="25"/>
+    </row>
+    <row r="201" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A201" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="B201" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="C201" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="29"/>
+      <c r="B202" s="29"/>
+      <c r="C202" s="29"/>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="30"/>
+      <c r="B203" s="30"/>
+      <c r="C203" s="30"/>
+    </row>
+    <row r="204" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A204" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="B204" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="C204" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="34"/>
+      <c r="B205" s="34"/>
+      <c r="C205" s="34"/>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="25"/>
+      <c r="B206" s="25"/>
+      <c r="C206" s="25"/>
+    </row>
+    <row r="207" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A207" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B207" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="C207" s="28">
+        <v>6256891.4800000004</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="29"/>
+      <c r="B208" s="29"/>
+      <c r="C208" s="29"/>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="30"/>
+      <c r="B209" s="30"/>
+      <c r="C209" s="30"/>
+    </row>
+    <row r="210" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A210" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="B210" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="C210" s="33">
+        <v>17285.71</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="34"/>
+      <c r="B211" s="34"/>
+      <c r="C211" s="34"/>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="25"/>
+      <c r="B212" s="25"/>
+      <c r="C212" s="25"/>
+    </row>
+    <row r="213" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A213" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="B213" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="C213" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="29"/>
+      <c r="B214" s="29"/>
+      <c r="C214" s="29"/>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="30"/>
+      <c r="B215" s="30"/>
+      <c r="C215" s="30"/>
+    </row>
+    <row r="216" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A216" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="B216" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="C216" s="33">
+        <v>203883.27</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="34"/>
+      <c r="B217" s="34"/>
+      <c r="C217" s="34"/>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="25"/>
+      <c r="B218" s="25"/>
+      <c r="C218" s="25"/>
+    </row>
+    <row r="219" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A219" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B219" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="C219" s="28">
+        <v>925466.57</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="29"/>
+      <c r="B220" s="29"/>
+      <c r="C220" s="29"/>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="30"/>
+      <c r="B221" s="30"/>
+      <c r="C221" s="30"/>
+    </row>
+    <row r="222" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A222" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="B222" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="C222" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="34"/>
+      <c r="B223" s="34"/>
+      <c r="C223" s="34"/>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="25"/>
+      <c r="B224" s="25"/>
+      <c r="C224" s="25"/>
+    </row>
+    <row r="225" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A225" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="B225" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C225" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="29"/>
+      <c r="B226" s="29"/>
+      <c r="C226" s="29"/>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="30"/>
+      <c r="B227" s="30"/>
+      <c r="C227" s="30"/>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="B228" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="C228" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="34"/>
+      <c r="B229" s="34"/>
+      <c r="C229" s="34"/>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="25"/>
+      <c r="B230" s="25"/>
+      <c r="C230" s="25"/>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="B231" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="C231" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="29"/>
+      <c r="B232" s="29"/>
+      <c r="C232" s="29"/>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="30"/>
+      <c r="B233" s="30"/>
+      <c r="C233" s="30"/>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="31" t="s">
+        <v>229</v>
+      </c>
+      <c r="B234" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="C234" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="34"/>
+      <c r="B235" s="34"/>
+      <c r="C235" s="34"/>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="25"/>
+      <c r="B236" s="25"/>
+      <c r="C236" s="25"/>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="B237" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="C237" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="29"/>
+      <c r="B238" s="29"/>
+      <c r="C238" s="29"/>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="30"/>
+      <c r="B239" s="30"/>
+      <c r="C239" s="30"/>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="B240" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="C240" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="34"/>
+      <c r="B241" s="34"/>
+      <c r="C241" s="34"/>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="25"/>
+      <c r="B242" s="25"/>
+      <c r="C242" s="25"/>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="B243" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C243" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="29"/>
+      <c r="B244" s="29"/>
+      <c r="C244" s="29"/>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="30"/>
+      <c r="B245" s="30"/>
+      <c r="C245" s="30"/>
+    </row>
+    <row r="246" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A246" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="B246" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="C246" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="34"/>
+      <c r="B247" s="34"/>
+      <c r="C247" s="34"/>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="25"/>
+      <c r="B248" s="25"/>
+      <c r="C248" s="25"/>
+    </row>
+    <row r="249" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A249" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="B249" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="C249" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="29"/>
+      <c r="B250" s="29"/>
+      <c r="C250" s="29"/>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="30"/>
+      <c r="B251" s="30"/>
+      <c r="C251" s="30"/>
+    </row>
+    <row r="252" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A252" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="B252" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="C252" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="34"/>
+      <c r="B253" s="34"/>
+      <c r="C253" s="34"/>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="25"/>
+      <c r="B254" s="25"/>
+      <c r="C254" s="25"/>
+    </row>
+    <row r="255" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A255" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="B255" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="C255" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="29"/>
+      <c r="B256" s="29"/>
+      <c r="C256" s="29"/>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="30"/>
+      <c r="B257" s="30"/>
+      <c r="C257" s="30"/>
+    </row>
+    <row r="258" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A258" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B258" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="C258" s="33">
+        <v>1131124.74</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="34"/>
+      <c r="B259" s="34"/>
+      <c r="C259" s="34"/>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="25"/>
+      <c r="B260" s="25"/>
+      <c r="C260" s="25"/>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B261" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="C261" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="29"/>
+      <c r="B262" s="29"/>
+      <c r="C262" s="29"/>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="30"/>
+      <c r="B263" s="30"/>
+      <c r="C263" s="30"/>
+    </row>
+    <row r="264" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A264" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="B264" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="C264" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="34"/>
+      <c r="B265" s="34"/>
+      <c r="C265" s="34"/>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="25"/>
+      <c r="B266" s="25"/>
+      <c r="C266" s="25"/>
+    </row>
+    <row r="267" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A267" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B267" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="C267" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="29"/>
+      <c r="B268" s="29"/>
+      <c r="C268" s="29"/>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="30"/>
+      <c r="B269" s="30"/>
+      <c r="C269" s="30"/>
+    </row>
+    <row r="270" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A270" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B270" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="C270" s="33">
+        <v>2459264.77</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="34"/>
+      <c r="B271" s="34"/>
+      <c r="C271" s="34"/>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="25"/>
+      <c r="B272" s="25"/>
+      <c r="C272" s="25"/>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="B273" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="C273" s="28">
+        <v>279805.15999999997</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="29"/>
+      <c r="B274" s="29"/>
+      <c r="C274" s="29"/>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="30"/>
+      <c r="B275" s="30"/>
+      <c r="C275" s="30"/>
+    </row>
+    <row r="276" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A276" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="B276" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="C276" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="34"/>
+      <c r="B277" s="34"/>
+      <c r="C277" s="34"/>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="25"/>
+      <c r="B278" s="25"/>
+      <c r="C278" s="25"/>
+    </row>
+    <row r="279" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A279" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B279" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="C279" s="28">
+        <v>1705937.66</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="29"/>
+      <c r="B280" s="29"/>
+      <c r="C280" s="29"/>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="30"/>
+      <c r="B281" s="30"/>
+      <c r="C281" s="30"/>
+    </row>
+    <row r="282" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A282" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="B282" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="C282" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="34"/>
+      <c r="B283" s="34"/>
+      <c r="C283" s="34"/>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="25"/>
+      <c r="B284" s="25"/>
+      <c r="C284" s="25"/>
+    </row>
+    <row r="285" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A285" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B285" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="C285" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="29"/>
+      <c r="B286" s="29"/>
+      <c r="C286" s="29"/>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="30"/>
+      <c r="B287" s="30"/>
+      <c r="C287" s="30"/>
+    </row>
+    <row r="288" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A288" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="B288" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="C288" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="34"/>
+      <c r="B289" s="34"/>
+      <c r="C289" s="34"/>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="25"/>
+      <c r="B290" s="25"/>
+      <c r="C290" s="25"/>
+    </row>
+    <row r="291" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A291" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B291" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C291" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="29"/>
+      <c r="B292" s="29"/>
+      <c r="C292" s="29"/>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="30"/>
+      <c r="B293" s="30"/>
+      <c r="C293" s="30"/>
+    </row>
+    <row r="294" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A294" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B294" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="C294" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="34"/>
+      <c r="B295" s="34"/>
+      <c r="C295" s="34"/>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="25"/>
+      <c r="B296" s="25"/>
+      <c r="C296" s="25"/>
+    </row>
+    <row r="297" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A297" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="B297" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C297" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="29"/>
+      <c r="B298" s="29"/>
+      <c r="C298" s="29"/>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="30"/>
+      <c r="B299" s="30"/>
+      <c r="C299" s="30"/>
+    </row>
+    <row r="300" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A300" s="31" t="s">
+        <v>268</v>
+      </c>
+      <c r="B300" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="C300" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="34"/>
+      <c r="B301" s="34"/>
+      <c r="C301" s="34"/>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="25"/>
+      <c r="B302" s="25"/>
+      <c r="C302" s="25"/>
+    </row>
+    <row r="303" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A303" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="B303" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="C303" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="29"/>
+      <c r="B304" s="29"/>
+      <c r="C304" s="29"/>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="30"/>
+      <c r="B305" s="30"/>
+      <c r="C305" s="30"/>
+    </row>
+    <row r="306" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A306" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="B306" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="C306" s="33">
+        <v>10232558.859999999</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="34"/>
+      <c r="B307" s="34"/>
+      <c r="C307" s="34"/>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="25"/>
+      <c r="B308" s="25"/>
+      <c r="C308" s="25"/>
+    </row>
+    <row r="309" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A309" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="B309" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="C309" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="29"/>
+      <c r="B310" s="29"/>
+      <c r="C310" s="29"/>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="30"/>
+      <c r="B311" s="30"/>
+      <c r="C311" s="30"/>
+    </row>
+    <row r="312" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A312" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="B312" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="C312" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="34"/>
+      <c r="B313" s="34"/>
+      <c r="C313" s="34"/>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="25"/>
+      <c r="B314" s="25"/>
+      <c r="C314" s="25"/>
+    </row>
+    <row r="315" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A315" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="B315" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="C315" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="29"/>
+      <c r="B316" s="29"/>
+      <c r="C316" s="29"/>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="30"/>
+      <c r="B317" s="30"/>
+      <c r="C317" s="30"/>
+    </row>
+    <row r="318" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A318" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="B318" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="C318" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="34"/>
+      <c r="B319" s="34"/>
+      <c r="C319" s="34"/>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="25"/>
+      <c r="B320" s="25"/>
+      <c r="C320" s="25"/>
+    </row>
+    <row r="321" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A321" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="B321" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="C321" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="29"/>
+      <c r="B322" s="29"/>
+      <c r="C322" s="29"/>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="30"/>
+      <c r="B323" s="30"/>
+      <c r="C323" s="30"/>
+    </row>
+    <row r="324" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A324" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="B324" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="C324" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="34"/>
+      <c r="B325" s="34"/>
+      <c r="C325" s="34"/>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="25"/>
+      <c r="B326" s="25"/>
+      <c r="C326" s="25"/>
+    </row>
+    <row r="327" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A327" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B327" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="C327" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="29"/>
+      <c r="B328" s="29"/>
+      <c r="C328" s="29"/>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="30"/>
+      <c r="B329" s="30"/>
+      <c r="C329" s="30"/>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="B330" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C330" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="34"/>
+      <c r="B331" s="34"/>
+      <c r="C331" s="34"/>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="25"/>
+      <c r="B332" s="25"/>
+      <c r="C332" s="25"/>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B333" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="C333" s="28">
+        <v>26114317.32</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="29"/>
+      <c r="B334" s="29"/>
+      <c r="C334" s="29"/>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="30"/>
+      <c r="B335" s="30"/>
+      <c r="C335" s="30"/>
+    </row>
+    <row r="336" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A336" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="B336" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="C336" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="34"/>
+      <c r="B337" s="34"/>
+      <c r="C337" s="34"/>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="25"/>
+      <c r="B338" s="25"/>
+      <c r="C338" s="25"/>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="B339" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="C339" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="29"/>
+      <c r="B340" s="29"/>
+      <c r="C340" s="29"/>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="30"/>
+      <c r="B341" s="30"/>
+      <c r="C341" s="30"/>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="B342" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="C342" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" s="34"/>
+      <c r="B343" s="34"/>
+      <c r="C343" s="34"/>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="36"/>
+      <c r="B344" s="36"/>
+      <c r="C344" s="36"/>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="B345" s="38" t="s">
+        <v>297</v>
+      </c>
+      <c r="C345" s="39">
+        <v>62367135.600000001</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">

--- a/공사 데이터 입력 자동화/6월_매출손익현황.xlsx
+++ b/공사 데이터 입력 자동화/6월_매출손익현황.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\조성현\Documents\GitHub\yjs_Dashboard\공사 데이터 입력 자동화\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074004F3-0B22-4668-B794-2E62D3B70ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00FC6FA-FF0B-4263-90E0-53B8C65F4DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-900" yWindow="1065" windowWidth="22620" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6월 공정현황" sheetId="2" r:id="rId1"/>
     <sheet name="6월 8일" sheetId="3" r:id="rId2"/>
     <sheet name="6월 9일" sheetId="4" r:id="rId3"/>
     <sheet name="6월 10일" sheetId="5" r:id="rId4"/>
+    <sheet name="6월 11일" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="303">
   <si>
     <t>JY25-256</t>
   </si>
@@ -2737,6 +2738,18 @@
   </si>
   <si>
     <t>JY26-043</t>
+  </si>
+  <si>
+    <t>JY26-059</t>
+  </si>
+  <si>
+    <t>고천동528 박희상 저압 신설</t>
+  </si>
+  <si>
+    <t>JY26-066</t>
+  </si>
+  <si>
+    <t>초평동622-2 이원섭 저압 신설</t>
   </si>
 </sst>
 </file>
@@ -2897,6 +2910,7 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -3601,11 +3615,11 @@
         <v>30000000</v>
       </c>
       <c r="E5" s="2">
-        <v>26114317.32</v>
+        <v>32829427.489999998</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" si="0"/>
-        <v>0.87047724400000004</v>
+        <v>1.0943142496666667</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -3661,11 +3675,11 @@
         <v>36994000</v>
       </c>
       <c r="E8" s="2">
-        <v>10232559</v>
+        <v>13381038.51</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
-        <v>0.27660050278423526</v>
+        <v>0.36170834486673514</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -3682,11 +3696,11 @@
         <v>1706000</v>
       </c>
       <c r="E9" s="2">
-        <v>1705938</v>
+        <v>1705937.66</v>
       </c>
       <c r="F9" s="3">
         <f t="shared" ref="F9:F25" si="1">E9/D9</f>
-        <v>0.99996365767878082</v>
+        <v>0.99996345838218048</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -3808,11 +3822,11 @@
         <v>2459000</v>
       </c>
       <c r="E15" s="2">
-        <v>2459265</v>
+        <v>2459264.77</v>
       </c>
       <c r="F15" s="3">
         <f t="shared" si="1"/>
-        <v>1.000107767385116</v>
+        <v>1.000107673851159</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -3829,11 +3843,11 @@
         <v>1131000</v>
       </c>
       <c r="E16" s="2">
-        <v>1131125</v>
+        <v>1131124.74</v>
       </c>
       <c r="F16" s="3">
         <f t="shared" si="1"/>
-        <v>1.0001105216622459</v>
+        <v>1.0001102917771882</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
@@ -3850,11 +3864,11 @@
         <v>1086000</v>
       </c>
       <c r="E17" s="2">
-        <v>1629648</v>
+        <v>1629647.99</v>
       </c>
       <c r="F17" s="3">
         <f t="shared" si="1"/>
-        <v>1.5005966850828729</v>
+        <v>1.5005966758747697</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
@@ -3913,11 +3927,11 @@
         <v>259000</v>
       </c>
       <c r="E20" s="2">
-        <v>203883</v>
+        <v>203883.27</v>
       </c>
       <c r="F20" s="3">
         <f t="shared" si="1"/>
-        <v>0.78719305019305019</v>
+        <v>0.78719409266409257</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
@@ -3934,11 +3948,11 @@
         <v>925000</v>
       </c>
       <c r="E21" s="2">
-        <v>925467</v>
+        <v>925466.57</v>
       </c>
       <c r="F21" s="3">
         <f t="shared" si="1"/>
-        <v>1.0005048648648649</v>
+        <v>1.0005043999999998</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
@@ -3955,11 +3969,11 @@
         <v>17000</v>
       </c>
       <c r="E22" s="2">
-        <v>17286</v>
+        <v>17285.71</v>
       </c>
       <c r="F22" s="3">
         <f t="shared" si="1"/>
-        <v>1.0168235294117647</v>
+        <v>1.0168064705882351</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
@@ -3976,11 +3990,11 @@
         <v>405000</v>
       </c>
       <c r="E23" s="2">
-        <v>405701</v>
+        <v>405701.07</v>
       </c>
       <c r="F23" s="3">
         <f t="shared" si="1"/>
-        <v>1.0017308641975309</v>
+        <v>1.0017310370370371</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
@@ -4157,11 +4171,11 @@
       </c>
       <c r="E32" s="6">
         <f>SUM(E4:E31)</f>
-        <v>54728904.399999999</v>
+        <v>64592492.860000007</v>
       </c>
       <c r="F32" s="7">
         <f>IF(D32&gt;0,E32/D32,"-")</f>
-        <v>0.12749890366919045</v>
+        <v>0.15047756053581832</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4202,7 +4216,7 @@
         <v>80</v>
       </c>
       <c r="E36" s="2">
-        <v>279805</v>
+        <v>279805.15999999997</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
@@ -4213,7 +4227,7 @@
         <v>81</v>
       </c>
       <c r="E37" s="2">
-        <v>6256891</v>
+        <v>6256891.4800000004</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
@@ -4227,7 +4241,7 @@
         <v>82</v>
       </c>
       <c r="E38" s="2">
-        <v>898036</v>
+        <v>898035.92</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
@@ -4248,13 +4262,29 @@
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E40" s="2"/>
+      <c r="A40" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="C40" t="s">
+        <v>300</v>
+      </c>
+      <c r="E40" s="2">
+        <v>507687.92</v>
+      </c>
       <c r="F40" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E41" s="2"/>
+      <c r="A41" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="C41" t="s">
+        <v>302</v>
+      </c>
+      <c r="E41" s="2">
+        <v>835486.55</v>
+      </c>
       <c r="F41" t="s">
         <v>14</v>
       </c>
@@ -4298,7 +4328,7 @@
       </c>
       <c r="E46" s="10">
         <f>SUM(E36:E45)</f>
-        <v>7638232</v>
+        <v>8981407.0300000012</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>14</v>
@@ -4327,11 +4357,11 @@
       </c>
       <c r="E48" s="12">
         <f>E32+E46</f>
-        <v>62367136.399999999</v>
+        <v>73573899.890000015</v>
       </c>
       <c r="F48" s="13">
         <f>E48/D48</f>
-        <v>0.1452932705882353</v>
+        <v>0.17140104808386725</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
@@ -11653,4 +11683,2486 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC5C1D8-3950-4A39-9E0E-EB4AB1040608}">
+  <dimension ref="A1:C352"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+    </row>
+    <row r="3" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+    </row>
+    <row r="6" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+    </row>
+    <row r="9" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+    </row>
+    <row r="15" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="28">
+        <v>203500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="35"/>
+      <c r="C18" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+    </row>
+    <row r="21" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+    </row>
+    <row r="24" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="34"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+    </row>
+    <row r="27" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+    </row>
+    <row r="30" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="34"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+    </row>
+    <row r="36" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="25"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+    </row>
+    <row r="39" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+    </row>
+    <row r="42" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="34"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="25"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+    </row>
+    <row r="45" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+    </row>
+    <row r="48" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="34"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="25"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+    </row>
+    <row r="51" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+    </row>
+    <row r="54" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="34"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="25"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25"/>
+    </row>
+    <row r="57" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C57" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="29"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+    </row>
+    <row r="60" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B60" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="C60" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="34"/>
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="25"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+    </row>
+    <row r="63" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="29"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="B66" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C66" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="34"/>
+      <c r="B67" s="34"/>
+      <c r="C67" s="34"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="25"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+    </row>
+    <row r="69" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="29"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
+    </row>
+    <row r="72" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="B72" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="C72" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="34"/>
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="25"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+    </row>
+    <row r="75" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C75" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="29"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="30"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="30"/>
+    </row>
+    <row r="78" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="C78" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="34"/>
+      <c r="B79" s="34"/>
+      <c r="C79" s="34"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="25"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+    </row>
+    <row r="81" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C81" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="29"/>
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="30"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
+    </row>
+    <row r="84" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C84" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="34"/>
+      <c r="B85" s="34"/>
+      <c r="C85" s="34"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="25"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+    </row>
+    <row r="87" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A87" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C87" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="29"/>
+      <c r="B88" s="29"/>
+      <c r="C88" s="29"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="30"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
+    </row>
+    <row r="90" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B90" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C90" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="34"/>
+      <c r="B91" s="34"/>
+      <c r="C91" s="34"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="25"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="25"/>
+    </row>
+    <row r="93" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A93" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B93" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C93" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="29"/>
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="30"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
+    </row>
+    <row r="96" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B96" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C96" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="34"/>
+      <c r="B97" s="34"/>
+      <c r="C97" s="34"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="25"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="25"/>
+    </row>
+    <row r="99" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A99" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B99" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="C99" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="29"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="29"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="30"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="30"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="B102" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C102" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="34"/>
+      <c r="B103" s="34"/>
+      <c r="C103" s="34"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="25"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="25"/>
+    </row>
+    <row r="105" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A105" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B105" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C105" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="29"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="29"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="30"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="30"/>
+    </row>
+    <row r="108" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A108" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B108" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="C108" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="34"/>
+      <c r="B109" s="34"/>
+      <c r="C109" s="34"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="25"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="25"/>
+    </row>
+    <row r="111" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A111" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B111" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C111" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="29"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="29"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="30"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="30"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="B114" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="C114" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="34"/>
+      <c r="B115" s="34"/>
+      <c r="C115" s="34"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="25"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="25"/>
+    </row>
+    <row r="117" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A117" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C117" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="29"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="29"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="30"/>
+    </row>
+    <row r="120" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A120" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B120" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C120" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="34"/>
+      <c r="B121" s="34"/>
+      <c r="C121" s="34"/>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="25"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="25"/>
+    </row>
+    <row r="123" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A123" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="B123" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="C123" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="29"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="29"/>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="30"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="30"/>
+    </row>
+    <row r="126" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A126" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B126" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="C126" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="34"/>
+      <c r="B127" s="34"/>
+      <c r="C127" s="34"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="25"/>
+      <c r="B128" s="25"/>
+      <c r="C128" s="25"/>
+    </row>
+    <row r="129" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="B129" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C129" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="29"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="29"/>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="30"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="30"/>
+    </row>
+    <row r="132" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A132" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="B132" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="C132" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="34"/>
+      <c r="B133" s="34"/>
+      <c r="C133" s="34"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="25"/>
+      <c r="B134" s="25"/>
+      <c r="C134" s="25"/>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="B135" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="C135" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="29"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="29"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="30"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="30"/>
+    </row>
+    <row r="138" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A138" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="B138" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C138" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="34"/>
+      <c r="B139" s="34"/>
+      <c r="C139" s="34"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="25"/>
+      <c r="B140" s="25"/>
+      <c r="C140" s="25"/>
+    </row>
+    <row r="141" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A141" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="B141" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="C141" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="29"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="29"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="30"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="30"/>
+    </row>
+    <row r="144" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A144" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B144" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C144" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="34"/>
+      <c r="B145" s="34"/>
+      <c r="C145" s="34"/>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="25"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="25"/>
+    </row>
+    <row r="147" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A147" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="B147" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C147" s="28">
+        <v>898035.92</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="29"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="29"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="30"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="30"/>
+    </row>
+    <row r="150" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A150" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B150" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="C150" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="34"/>
+      <c r="B151" s="34"/>
+      <c r="C151" s="34"/>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="25"/>
+      <c r="B152" s="25"/>
+      <c r="C152" s="25"/>
+    </row>
+    <row r="153" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A153" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="B153" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C153" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="29"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="29"/>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="30"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="30"/>
+    </row>
+    <row r="156" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A156" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="B156" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C156" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="34"/>
+      <c r="B157" s="34"/>
+      <c r="C157" s="34"/>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="25"/>
+      <c r="B158" s="25"/>
+      <c r="C158" s="25"/>
+    </row>
+    <row r="159" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A159" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="B159" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="C159" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="29"/>
+      <c r="B160" s="29"/>
+      <c r="C160" s="29"/>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="30"/>
+      <c r="B161" s="30"/>
+      <c r="C161" s="30"/>
+    </row>
+    <row r="162" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A162" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="B162" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="C162" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="34"/>
+      <c r="B163" s="34"/>
+      <c r="C163" s="34"/>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="25"/>
+      <c r="B164" s="25"/>
+      <c r="C164" s="25"/>
+    </row>
+    <row r="165" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A165" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="B165" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="C165" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="29"/>
+      <c r="B166" s="29"/>
+      <c r="C166" s="29"/>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="30"/>
+      <c r="B167" s="30"/>
+      <c r="C167" s="30"/>
+    </row>
+    <row r="168" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A168" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="B168" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="C168" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="34"/>
+      <c r="B169" s="34"/>
+      <c r="C169" s="34"/>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="25"/>
+      <c r="B170" s="25"/>
+      <c r="C170" s="25"/>
+    </row>
+    <row r="171" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A171" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="B171" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C171" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="29"/>
+      <c r="B172" s="29"/>
+      <c r="C172" s="29"/>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="30"/>
+      <c r="B173" s="30"/>
+      <c r="C173" s="30"/>
+    </row>
+    <row r="174" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A174" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="B174" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C174" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="34"/>
+      <c r="B175" s="34"/>
+      <c r="C175" s="34"/>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="25"/>
+      <c r="B176" s="25"/>
+      <c r="C176" s="25"/>
+    </row>
+    <row r="177" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A177" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="B177" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C177" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
+      <c r="C178" s="29"/>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="30"/>
+      <c r="B179" s="30"/>
+      <c r="C179" s="30"/>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="B180" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C180" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="34"/>
+      <c r="B181" s="34"/>
+      <c r="C181" s="34"/>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="25"/>
+      <c r="B182" s="25"/>
+      <c r="C182" s="25"/>
+    </row>
+    <row r="183" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A183" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="B183" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C183" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="29"/>
+      <c r="B184" s="29"/>
+      <c r="C184" s="29"/>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="30"/>
+      <c r="B185" s="30"/>
+      <c r="C185" s="30"/>
+    </row>
+    <row r="186" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A186" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="B186" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="C186" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="34"/>
+      <c r="B187" s="34"/>
+      <c r="C187" s="34"/>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="25"/>
+      <c r="B188" s="25"/>
+      <c r="C188" s="25"/>
+    </row>
+    <row r="189" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A189" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="B189" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="C189" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="29"/>
+      <c r="B190" s="29"/>
+      <c r="C190" s="29"/>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="30"/>
+      <c r="B191" s="30"/>
+      <c r="C191" s="30"/>
+    </row>
+    <row r="192" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A192" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="B192" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C192" s="33">
+        <v>405701.07</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="34"/>
+      <c r="B193" s="34"/>
+      <c r="C193" s="34"/>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="25"/>
+      <c r="B194" s="25"/>
+      <c r="C194" s="25"/>
+    </row>
+    <row r="195" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A195" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="B195" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C195" s="28">
+        <v>9903715.0800000001</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="29"/>
+      <c r="B196" s="29"/>
+      <c r="C196" s="29"/>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="30"/>
+      <c r="B197" s="30"/>
+      <c r="C197" s="30"/>
+    </row>
+    <row r="198" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A198" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B198" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="C198" s="33">
+        <v>1629647.99</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="34"/>
+      <c r="B199" s="34"/>
+      <c r="C199" s="34"/>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="25"/>
+      <c r="B200" s="25"/>
+      <c r="C200" s="25"/>
+    </row>
+    <row r="201" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A201" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="B201" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="C201" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="29"/>
+      <c r="B202" s="29"/>
+      <c r="C202" s="29"/>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="30"/>
+      <c r="B203" s="30"/>
+      <c r="C203" s="30"/>
+    </row>
+    <row r="204" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A204" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="B204" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="C204" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="34"/>
+      <c r="B205" s="34"/>
+      <c r="C205" s="34"/>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="25"/>
+      <c r="B206" s="25"/>
+      <c r="C206" s="25"/>
+    </row>
+    <row r="207" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A207" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B207" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="C207" s="28">
+        <v>6256891.4800000004</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="29"/>
+      <c r="B208" s="29"/>
+      <c r="C208" s="29"/>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="30"/>
+      <c r="B209" s="30"/>
+      <c r="C209" s="30"/>
+    </row>
+    <row r="210" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A210" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="B210" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="C210" s="33">
+        <v>17285.71</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="34"/>
+      <c r="B211" s="34"/>
+      <c r="C211" s="34"/>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="25"/>
+      <c r="B212" s="25"/>
+      <c r="C212" s="25"/>
+    </row>
+    <row r="213" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A213" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="B213" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="C213" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="29"/>
+      <c r="B214" s="29"/>
+      <c r="C214" s="29"/>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="30"/>
+      <c r="B215" s="30"/>
+      <c r="C215" s="30"/>
+    </row>
+    <row r="216" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A216" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="B216" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="C216" s="33">
+        <v>203883.27</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="34"/>
+      <c r="B217" s="34"/>
+      <c r="C217" s="34"/>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="25"/>
+      <c r="B218" s="25"/>
+      <c r="C218" s="25"/>
+    </row>
+    <row r="219" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A219" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B219" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="C219" s="28">
+        <v>925466.57</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="29"/>
+      <c r="B220" s="29"/>
+      <c r="C220" s="29"/>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="30"/>
+      <c r="B221" s="30"/>
+      <c r="C221" s="30"/>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="B222" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="C222" s="33">
+        <v>507687.92</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="34"/>
+      <c r="B223" s="34"/>
+      <c r="C223" s="34"/>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="25"/>
+      <c r="B224" s="25"/>
+      <c r="C224" s="25"/>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="B225" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C225" s="28">
+        <v>835486.55</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="29"/>
+      <c r="B226" s="29"/>
+      <c r="C226" s="29"/>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="30"/>
+      <c r="B227" s="30"/>
+      <c r="C227" s="30"/>
+    </row>
+    <row r="228" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A228" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="B228" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="C228" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="34"/>
+      <c r="B229" s="34"/>
+      <c r="C229" s="34"/>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="25"/>
+      <c r="B230" s="25"/>
+      <c r="C230" s="25"/>
+    </row>
+    <row r="231" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A231" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="B231" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C231" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="29"/>
+      <c r="B232" s="29"/>
+      <c r="C232" s="29"/>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="30"/>
+      <c r="B233" s="30"/>
+      <c r="C233" s="30"/>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="B234" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="C234" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="34"/>
+      <c r="B235" s="34"/>
+      <c r="C235" s="34"/>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="25"/>
+      <c r="B236" s="25"/>
+      <c r="C236" s="25"/>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="B237" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="C237" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="29"/>
+      <c r="B238" s="29"/>
+      <c r="C238" s="29"/>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="30"/>
+      <c r="B239" s="30"/>
+      <c r="C239" s="30"/>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="31" t="s">
+        <v>229</v>
+      </c>
+      <c r="B240" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="C240" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="34"/>
+      <c r="B241" s="34"/>
+      <c r="C241" s="34"/>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="25"/>
+      <c r="B242" s="25"/>
+      <c r="C242" s="25"/>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="B243" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="C243" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="29"/>
+      <c r="B244" s="29"/>
+      <c r="C244" s="29"/>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="30"/>
+      <c r="B245" s="30"/>
+      <c r="C245" s="30"/>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="B246" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="C246" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="34"/>
+      <c r="B247" s="34"/>
+      <c r="C247" s="34"/>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="25"/>
+      <c r="B248" s="25"/>
+      <c r="C248" s="25"/>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="B249" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C249" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="29"/>
+      <c r="B250" s="29"/>
+      <c r="C250" s="29"/>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="30"/>
+      <c r="B251" s="30"/>
+      <c r="C251" s="30"/>
+    </row>
+    <row r="252" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A252" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="B252" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="C252" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="34"/>
+      <c r="B253" s="34"/>
+      <c r="C253" s="34"/>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="25"/>
+      <c r="B254" s="25"/>
+      <c r="C254" s="25"/>
+    </row>
+    <row r="255" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A255" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="B255" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="C255" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="29"/>
+      <c r="B256" s="29"/>
+      <c r="C256" s="29"/>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="30"/>
+      <c r="B257" s="30"/>
+      <c r="C257" s="30"/>
+    </row>
+    <row r="258" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A258" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="B258" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="C258" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="34"/>
+      <c r="B259" s="34"/>
+      <c r="C259" s="34"/>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="25"/>
+      <c r="B260" s="25"/>
+      <c r="C260" s="25"/>
+    </row>
+    <row r="261" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A261" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="B261" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="C261" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="29"/>
+      <c r="B262" s="29"/>
+      <c r="C262" s="29"/>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="30"/>
+      <c r="B263" s="30"/>
+      <c r="C263" s="30"/>
+    </row>
+    <row r="264" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A264" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B264" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="C264" s="33">
+        <v>1131124.74</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="34"/>
+      <c r="B265" s="34"/>
+      <c r="C265" s="34"/>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="25"/>
+      <c r="B266" s="25"/>
+      <c r="C266" s="25"/>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B267" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="C267" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="29"/>
+      <c r="B268" s="29"/>
+      <c r="C268" s="29"/>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="30"/>
+      <c r="B269" s="30"/>
+      <c r="C269" s="30"/>
+    </row>
+    <row r="270" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A270" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="B270" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="C270" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="34"/>
+      <c r="B271" s="34"/>
+      <c r="C271" s="34"/>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="25"/>
+      <c r="B272" s="25"/>
+      <c r="C272" s="25"/>
+    </row>
+    <row r="273" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A273" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B273" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="C273" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="29"/>
+      <c r="B274" s="29"/>
+      <c r="C274" s="29"/>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="30"/>
+      <c r="B275" s="30"/>
+      <c r="C275" s="30"/>
+    </row>
+    <row r="276" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A276" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B276" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="C276" s="33">
+        <v>2459264.77</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="34"/>
+      <c r="B277" s="34"/>
+      <c r="C277" s="34"/>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="25"/>
+      <c r="B278" s="25"/>
+      <c r="C278" s="25"/>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="B279" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="C279" s="28">
+        <v>279805.15999999997</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="29"/>
+      <c r="B280" s="29"/>
+      <c r="C280" s="29"/>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="30"/>
+      <c r="B281" s="30"/>
+      <c r="C281" s="30"/>
+    </row>
+    <row r="282" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A282" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="B282" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="C282" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="34"/>
+      <c r="B283" s="34"/>
+      <c r="C283" s="34"/>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="25"/>
+      <c r="B284" s="25"/>
+      <c r="C284" s="25"/>
+    </row>
+    <row r="285" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A285" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B285" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="C285" s="28">
+        <v>1705937.66</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="29"/>
+      <c r="B286" s="29"/>
+      <c r="C286" s="29"/>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="30"/>
+      <c r="B287" s="30"/>
+      <c r="C287" s="30"/>
+    </row>
+    <row r="288" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A288" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="B288" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="C288" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="34"/>
+      <c r="B289" s="34"/>
+      <c r="C289" s="34"/>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="25"/>
+      <c r="B290" s="25"/>
+      <c r="C290" s="25"/>
+    </row>
+    <row r="291" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A291" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B291" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="C291" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="29"/>
+      <c r="B292" s="29"/>
+      <c r="C292" s="29"/>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="30"/>
+      <c r="B293" s="30"/>
+      <c r="C293" s="30"/>
+    </row>
+    <row r="294" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A294" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="B294" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="C294" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="34"/>
+      <c r="B295" s="34"/>
+      <c r="C295" s="34"/>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="25"/>
+      <c r="B296" s="25"/>
+      <c r="C296" s="25"/>
+    </row>
+    <row r="297" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A297" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B297" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C297" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="29"/>
+      <c r="B298" s="29"/>
+      <c r="C298" s="29"/>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="30"/>
+      <c r="B299" s="30"/>
+      <c r="C299" s="30"/>
+    </row>
+    <row r="300" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A300" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B300" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="C300" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="34"/>
+      <c r="B301" s="34"/>
+      <c r="C301" s="34"/>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="25"/>
+      <c r="B302" s="25"/>
+      <c r="C302" s="25"/>
+    </row>
+    <row r="303" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A303" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="B303" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C303" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="29"/>
+      <c r="B304" s="29"/>
+      <c r="C304" s="29"/>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="30"/>
+      <c r="B305" s="30"/>
+      <c r="C305" s="30"/>
+    </row>
+    <row r="306" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A306" s="31" t="s">
+        <v>268</v>
+      </c>
+      <c r="B306" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="C306" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="34"/>
+      <c r="B307" s="34"/>
+      <c r="C307" s="34"/>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="25"/>
+      <c r="B308" s="25"/>
+      <c r="C308" s="25"/>
+    </row>
+    <row r="309" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A309" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="B309" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="C309" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="29"/>
+      <c r="B310" s="29"/>
+      <c r="C310" s="29"/>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="30"/>
+      <c r="B311" s="30"/>
+      <c r="C311" s="30"/>
+    </row>
+    <row r="312" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A312" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="B312" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="C312" s="33">
+        <v>13381038.51</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="34"/>
+      <c r="B313" s="34"/>
+      <c r="C313" s="34"/>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="25"/>
+      <c r="B314" s="25"/>
+      <c r="C314" s="25"/>
+    </row>
+    <row r="315" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A315" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="B315" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="C315" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="29"/>
+      <c r="B316" s="29"/>
+      <c r="C316" s="29"/>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="30"/>
+      <c r="B317" s="30"/>
+      <c r="C317" s="30"/>
+    </row>
+    <row r="318" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A318" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="B318" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="C318" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="34"/>
+      <c r="B319" s="34"/>
+      <c r="C319" s="34"/>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="25"/>
+      <c r="B320" s="25"/>
+      <c r="C320" s="25"/>
+    </row>
+    <row r="321" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A321" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="B321" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="C321" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="29"/>
+      <c r="B322" s="29"/>
+      <c r="C322" s="29"/>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="30"/>
+      <c r="B323" s="30"/>
+      <c r="C323" s="30"/>
+    </row>
+    <row r="324" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A324" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="B324" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="C324" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="34"/>
+      <c r="B325" s="34"/>
+      <c r="C325" s="34"/>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="25"/>
+      <c r="B326" s="25"/>
+      <c r="C326" s="25"/>
+    </row>
+    <row r="327" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A327" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="B327" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="C327" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="29"/>
+      <c r="B328" s="29"/>
+      <c r="C328" s="29"/>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="30"/>
+      <c r="B329" s="30"/>
+      <c r="C329" s="30"/>
+    </row>
+    <row r="330" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A330" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="B330" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="C330" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="34"/>
+      <c r="B331" s="34"/>
+      <c r="C331" s="34"/>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="25"/>
+      <c r="B332" s="25"/>
+      <c r="C332" s="25"/>
+    </row>
+    <row r="333" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A333" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B333" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="C333" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="29"/>
+      <c r="B334" s="29"/>
+      <c r="C334" s="29"/>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="30"/>
+      <c r="B335" s="30"/>
+      <c r="C335" s="30"/>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="B336" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C336" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="34"/>
+      <c r="B337" s="34"/>
+      <c r="C337" s="34"/>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="25"/>
+      <c r="B338" s="25"/>
+      <c r="C338" s="25"/>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B339" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="C339" s="28">
+        <v>32829427.489999998</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="29"/>
+      <c r="B340" s="29"/>
+      <c r="C340" s="29"/>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="30"/>
+      <c r="B341" s="30"/>
+      <c r="C341" s="30"/>
+    </row>
+    <row r="342" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A342" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="B342" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="C342" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" s="34"/>
+      <c r="B343" s="34"/>
+      <c r="C343" s="34"/>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="25"/>
+      <c r="B344" s="25"/>
+      <c r="C344" s="25"/>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="B345" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="C345" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="29"/>
+      <c r="B346" s="29"/>
+      <c r="C346" s="29"/>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="30"/>
+      <c r="B347" s="30"/>
+      <c r="C347" s="30"/>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="B348" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="C348" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="34"/>
+      <c r="B349" s="34"/>
+      <c r="C349" s="34"/>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="36"/>
+      <c r="B350" s="36"/>
+      <c r="C350" s="36"/>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="B351" s="38" t="s">
+        <v>297</v>
+      </c>
+      <c r="C351" s="39">
+        <v>73573899.890000001</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="40"/>
+      <c r="B352" s="40"/>
+      <c r="C352" s="40"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/공사 데이터 입력 자동화/6월_매출손익현황.xlsx
+++ b/공사 데이터 입력 자동화/6월_매출손익현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\조성현\Documents\GitHub\yjs_Dashboard\공사 데이터 입력 자동화\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00FC6FA-FF0B-4263-90E0-53B8C65F4DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A52062E-D6AB-4677-B26D-1AD56D8D4452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2070" yWindow="420" windowWidth="22620" windowHeight="14805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6월 공정현황" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="6월 9일" sheetId="4" r:id="rId3"/>
     <sheet name="6월 10일" sheetId="5" r:id="rId4"/>
     <sheet name="6월 11일" sheetId="6" r:id="rId5"/>
+    <sheet name="6월 12일" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="305">
   <si>
     <t>JY25-256</t>
   </si>
@@ -2750,6 +2751,12 @@
   </si>
   <si>
     <t>초평동622-2 이원섭 저압 신설</t>
+  </si>
+  <si>
+    <t>JY25-260</t>
+  </si>
+  <si>
+    <t>안양동 413-1 (주)대영플러스 일반용(갑)저압 120Kw 신설 외 1</t>
   </si>
 </sst>
 </file>
@@ -3615,11 +3622,11 @@
         <v>30000000</v>
       </c>
       <c r="E5" s="2">
-        <v>32829427.489999998</v>
+        <v>37306167.600000001</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" si="0"/>
-        <v>1.0943142496666667</v>
+        <v>1.24353892</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -4032,11 +4039,11 @@
         <v>1002000</v>
       </c>
       <c r="E25" s="2">
-        <v>0</v>
+        <v>1575342.96</v>
       </c>
       <c r="F25" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.5721985628742514</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
@@ -4095,11 +4102,11 @@
         <v>7472000</v>
       </c>
       <c r="E28" s="2">
-        <v>0</v>
+        <v>4035280.68</v>
       </c>
       <c r="F28" s="3">
         <f>E28/D28</f>
-        <v>0</v>
+        <v>0.5400536241970022</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
@@ -4171,11 +4178,11 @@
       </c>
       <c r="E32" s="6">
         <f>SUM(E4:E31)</f>
-        <v>64592492.860000007</v>
+        <v>74679856.610000014</v>
       </c>
       <c r="F32" s="7">
         <f>IF(D32&gt;0,E32/D32,"-")</f>
-        <v>0.15047756053581832</v>
+        <v>0.17397753432731511</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4357,11 +4364,11 @@
       </c>
       <c r="E48" s="12">
         <f>E32+E46</f>
-        <v>73573899.890000015</v>
+        <v>83661263.640000015</v>
       </c>
       <c r="F48" s="13">
         <f>E48/D48</f>
-        <v>0.17140104808386725</v>
+        <v>0.19490102187536404</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
@@ -14165,4 +14172,2507 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A83B120-DF0E-482F-A671-B91FA1F387E8}">
+  <dimension ref="A1:C355"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+    </row>
+    <row r="3" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+    </row>
+    <row r="6" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+    </row>
+    <row r="9" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+    </row>
+    <row r="15" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="28">
+        <v>203500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="35"/>
+      <c r="C18" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+    </row>
+    <row r="21" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+    </row>
+    <row r="24" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="34"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+    </row>
+    <row r="27" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+    </row>
+    <row r="30" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="34"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+    </row>
+    <row r="36" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="25"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+    </row>
+    <row r="39" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+    </row>
+    <row r="42" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="34"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="25"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+    </row>
+    <row r="45" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+    </row>
+    <row r="48" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="34"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="25"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+    </row>
+    <row r="51" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+    </row>
+    <row r="54" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="34"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="25"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25"/>
+    </row>
+    <row r="57" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C57" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="29"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+    </row>
+    <row r="60" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B60" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="C60" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="34"/>
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="25"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+    </row>
+    <row r="63" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" s="28">
+        <v>1575342.96</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="29"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="B66" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C66" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="34"/>
+      <c r="B67" s="34"/>
+      <c r="C67" s="34"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="25"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+    </row>
+    <row r="69" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="29"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
+    </row>
+    <row r="72" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="B72" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="C72" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="34"/>
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="25"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+    </row>
+    <row r="75" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C75" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="29"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="30"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="30"/>
+    </row>
+    <row r="78" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="C78" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="34"/>
+      <c r="B79" s="34"/>
+      <c r="C79" s="34"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="25"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+    </row>
+    <row r="81" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C81" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="29"/>
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="30"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
+    </row>
+    <row r="84" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C84" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="34"/>
+      <c r="B85" s="34"/>
+      <c r="C85" s="34"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="25"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+    </row>
+    <row r="87" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A87" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C87" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="29"/>
+      <c r="B88" s="29"/>
+      <c r="C88" s="29"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="30"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
+    </row>
+    <row r="90" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B90" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C90" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="34"/>
+      <c r="B91" s="34"/>
+      <c r="C91" s="34"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="25"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="25"/>
+    </row>
+    <row r="93" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A93" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B93" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C93" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="29"/>
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="30"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
+    </row>
+    <row r="96" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B96" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C96" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="34"/>
+      <c r="B97" s="34"/>
+      <c r="C97" s="34"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="25"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="25"/>
+    </row>
+    <row r="99" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A99" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B99" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="C99" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="29"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="29"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="30"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="30"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="B102" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C102" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="34"/>
+      <c r="B103" s="34"/>
+      <c r="C103" s="34"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="25"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="25"/>
+    </row>
+    <row r="105" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A105" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B105" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C105" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="29"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="29"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="30"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="30"/>
+    </row>
+    <row r="108" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A108" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B108" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="C108" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="34"/>
+      <c r="B109" s="34"/>
+      <c r="C109" s="34"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="25"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="25"/>
+    </row>
+    <row r="111" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A111" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B111" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C111" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="29"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="29"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="30"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="30"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="B114" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="C114" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="34"/>
+      <c r="B115" s="34"/>
+      <c r="C115" s="34"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="25"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="25"/>
+    </row>
+    <row r="117" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A117" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C117" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="29"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="29"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="30"/>
+    </row>
+    <row r="120" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A120" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B120" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C120" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="34"/>
+      <c r="B121" s="34"/>
+      <c r="C121" s="34"/>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="25"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="25"/>
+    </row>
+    <row r="123" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A123" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="B123" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="C123" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="29"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="29"/>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="30"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="30"/>
+    </row>
+    <row r="126" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A126" s="31" t="s">
+        <v>303</v>
+      </c>
+      <c r="B126" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="C126" s="33">
+        <v>4035280.68</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="34"/>
+      <c r="B127" s="34"/>
+      <c r="C127" s="34"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="25"/>
+      <c r="B128" s="25"/>
+      <c r="C128" s="25"/>
+    </row>
+    <row r="129" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="B129" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="C129" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="29"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="29"/>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="30"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="30"/>
+    </row>
+    <row r="132" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A132" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="B132" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="C132" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="34"/>
+      <c r="B133" s="34"/>
+      <c r="C133" s="34"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="25"/>
+      <c r="B134" s="25"/>
+      <c r="C134" s="25"/>
+    </row>
+    <row r="135" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A135" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="B135" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="C135" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="29"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="29"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="30"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="30"/>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="B138" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="C138" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="34"/>
+      <c r="B139" s="34"/>
+      <c r="C139" s="34"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="25"/>
+      <c r="B140" s="25"/>
+      <c r="C140" s="25"/>
+    </row>
+    <row r="141" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A141" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="B141" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="C141" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="29"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="29"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="30"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="30"/>
+    </row>
+    <row r="144" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A144" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B144" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="C144" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="34"/>
+      <c r="B145" s="34"/>
+      <c r="C145" s="34"/>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="25"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="25"/>
+    </row>
+    <row r="147" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A147" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="B147" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C147" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="29"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="29"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="30"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="30"/>
+    </row>
+    <row r="150" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A150" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="B150" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="C150" s="33">
+        <v>898035.92</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="34"/>
+      <c r="B151" s="34"/>
+      <c r="C151" s="34"/>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="25"/>
+      <c r="B152" s="25"/>
+      <c r="C152" s="25"/>
+    </row>
+    <row r="153" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A153" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="B153" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C153" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="29"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="29"/>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="30"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="30"/>
+    </row>
+    <row r="156" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A156" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="B156" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="C156" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="34"/>
+      <c r="B157" s="34"/>
+      <c r="C157" s="34"/>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="25"/>
+      <c r="B158" s="25"/>
+      <c r="C158" s="25"/>
+    </row>
+    <row r="159" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A159" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="B159" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C159" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="29"/>
+      <c r="B160" s="29"/>
+      <c r="C160" s="29"/>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="30"/>
+      <c r="B161" s="30"/>
+      <c r="C161" s="30"/>
+    </row>
+    <row r="162" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A162" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="B162" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="C162" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="34"/>
+      <c r="B163" s="34"/>
+      <c r="C163" s="34"/>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="25"/>
+      <c r="B164" s="25"/>
+      <c r="C164" s="25"/>
+    </row>
+    <row r="165" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A165" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="B165" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="C165" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="29"/>
+      <c r="B166" s="29"/>
+      <c r="C166" s="29"/>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="30"/>
+      <c r="B167" s="30"/>
+      <c r="C167" s="30"/>
+    </row>
+    <row r="168" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A168" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="B168" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="C168" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="34"/>
+      <c r="B169" s="34"/>
+      <c r="C169" s="34"/>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="25"/>
+      <c r="B170" s="25"/>
+      <c r="C170" s="25"/>
+    </row>
+    <row r="171" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A171" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="B171" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="C171" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="29"/>
+      <c r="B172" s="29"/>
+      <c r="C172" s="29"/>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="30"/>
+      <c r="B173" s="30"/>
+      <c r="C173" s="30"/>
+    </row>
+    <row r="174" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A174" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="B174" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C174" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="34"/>
+      <c r="B175" s="34"/>
+      <c r="C175" s="34"/>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="25"/>
+      <c r="B176" s="25"/>
+      <c r="C176" s="25"/>
+    </row>
+    <row r="177" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A177" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B177" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="C177" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
+      <c r="C178" s="29"/>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="30"/>
+      <c r="B179" s="30"/>
+      <c r="C179" s="30"/>
+    </row>
+    <row r="180" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A180" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B180" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C180" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="34"/>
+      <c r="B181" s="34"/>
+      <c r="C181" s="34"/>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="25"/>
+      <c r="B182" s="25"/>
+      <c r="C182" s="25"/>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="B183" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="C183" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="29"/>
+      <c r="B184" s="29"/>
+      <c r="C184" s="29"/>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="30"/>
+      <c r="B185" s="30"/>
+      <c r="C185" s="30"/>
+    </row>
+    <row r="186" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A186" s="31" t="s">
+        <v>200</v>
+      </c>
+      <c r="B186" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="C186" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="34"/>
+      <c r="B187" s="34"/>
+      <c r="C187" s="34"/>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="25"/>
+      <c r="B188" s="25"/>
+      <c r="C188" s="25"/>
+    </row>
+    <row r="189" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A189" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="B189" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="C189" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="29"/>
+      <c r="B190" s="29"/>
+      <c r="C190" s="29"/>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="30"/>
+      <c r="B191" s="30"/>
+      <c r="C191" s="30"/>
+    </row>
+    <row r="192" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A192" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="B192" s="32" t="s">
+        <v>205</v>
+      </c>
+      <c r="C192" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="34"/>
+      <c r="B193" s="34"/>
+      <c r="C193" s="34"/>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="25"/>
+      <c r="B194" s="25"/>
+      <c r="C194" s="25"/>
+    </row>
+    <row r="195" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A195" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="B195" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C195" s="28">
+        <v>405701.07</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="29"/>
+      <c r="B196" s="29"/>
+      <c r="C196" s="29"/>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="30"/>
+      <c r="B197" s="30"/>
+      <c r="C197" s="30"/>
+    </row>
+    <row r="198" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A198" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="B198" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C198" s="33">
+        <v>9903715.0800000001</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="34"/>
+      <c r="B199" s="34"/>
+      <c r="C199" s="34"/>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="25"/>
+      <c r="B200" s="25"/>
+      <c r="C200" s="25"/>
+    </row>
+    <row r="201" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A201" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B201" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="C201" s="28">
+        <v>1629647.99</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="29"/>
+      <c r="B202" s="29"/>
+      <c r="C202" s="29"/>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="30"/>
+      <c r="B203" s="30"/>
+      <c r="C203" s="30"/>
+    </row>
+    <row r="204" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A204" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="B204" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="C204" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="34"/>
+      <c r="B205" s="34"/>
+      <c r="C205" s="34"/>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="25"/>
+      <c r="B206" s="25"/>
+      <c r="C206" s="25"/>
+    </row>
+    <row r="207" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A207" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="B207" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="C207" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="29"/>
+      <c r="B208" s="29"/>
+      <c r="C208" s="29"/>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="30"/>
+      <c r="B209" s="30"/>
+      <c r="C209" s="30"/>
+    </row>
+    <row r="210" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A210" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="B210" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="C210" s="33">
+        <v>6256891.4800000004</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="34"/>
+      <c r="B211" s="34"/>
+      <c r="C211" s="34"/>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="25"/>
+      <c r="B212" s="25"/>
+      <c r="C212" s="25"/>
+    </row>
+    <row r="213" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A213" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="B213" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="C213" s="28">
+        <v>17285.71</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="29"/>
+      <c r="B214" s="29"/>
+      <c r="C214" s="29"/>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="30"/>
+      <c r="B215" s="30"/>
+      <c r="C215" s="30"/>
+    </row>
+    <row r="216" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A216" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="B216" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="C216" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="34"/>
+      <c r="B217" s="34"/>
+      <c r="C217" s="34"/>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="25"/>
+      <c r="B218" s="25"/>
+      <c r="C218" s="25"/>
+    </row>
+    <row r="219" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A219" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="B219" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="C219" s="28">
+        <v>203883.27</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="29"/>
+      <c r="B220" s="29"/>
+      <c r="C220" s="29"/>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="30"/>
+      <c r="B221" s="30"/>
+      <c r="C221" s="30"/>
+    </row>
+    <row r="222" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A222" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B222" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="C222" s="33">
+        <v>925466.57</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="34"/>
+      <c r="B223" s="34"/>
+      <c r="C223" s="34"/>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="25"/>
+      <c r="B224" s="25"/>
+      <c r="C224" s="25"/>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="B225" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C225" s="28">
+        <v>507687.92</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="29"/>
+      <c r="B226" s="29"/>
+      <c r="C226" s="29"/>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="30"/>
+      <c r="B227" s="30"/>
+      <c r="C227" s="30"/>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="B228" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="C228" s="33">
+        <v>835486.55</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="34"/>
+      <c r="B229" s="34"/>
+      <c r="C229" s="34"/>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="25"/>
+      <c r="B230" s="25"/>
+      <c r="C230" s="25"/>
+    </row>
+    <row r="231" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A231" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="B231" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="C231" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="29"/>
+      <c r="B232" s="29"/>
+      <c r="C232" s="29"/>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="30"/>
+      <c r="B233" s="30"/>
+      <c r="C233" s="30"/>
+    </row>
+    <row r="234" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A234" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="B234" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="C234" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="34"/>
+      <c r="B235" s="34"/>
+      <c r="C235" s="34"/>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="25"/>
+      <c r="B236" s="25"/>
+      <c r="C236" s="25"/>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="B237" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C237" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="29"/>
+      <c r="B238" s="29"/>
+      <c r="C238" s="29"/>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="30"/>
+      <c r="B239" s="30"/>
+      <c r="C239" s="30"/>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="31" t="s">
+        <v>227</v>
+      </c>
+      <c r="B240" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="C240" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="34"/>
+      <c r="B241" s="34"/>
+      <c r="C241" s="34"/>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="25"/>
+      <c r="B242" s="25"/>
+      <c r="C242" s="25"/>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="B243" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="C243" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="29"/>
+      <c r="B244" s="29"/>
+      <c r="C244" s="29"/>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="30"/>
+      <c r="B245" s="30"/>
+      <c r="C245" s="30"/>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="B246" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="C246" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="34"/>
+      <c r="B247" s="34"/>
+      <c r="C247" s="34"/>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="25"/>
+      <c r="B248" s="25"/>
+      <c r="C248" s="25"/>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="B249" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="C249" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="29"/>
+      <c r="B250" s="29"/>
+      <c r="C250" s="29"/>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="30"/>
+      <c r="B251" s="30"/>
+      <c r="C251" s="30"/>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="B252" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="C252" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="34"/>
+      <c r="B253" s="34"/>
+      <c r="C253" s="34"/>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="25"/>
+      <c r="B254" s="25"/>
+      <c r="C254" s="25"/>
+    </row>
+    <row r="255" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A255" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="B255" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="C255" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="29"/>
+      <c r="B256" s="29"/>
+      <c r="C256" s="29"/>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="30"/>
+      <c r="B257" s="30"/>
+      <c r="C257" s="30"/>
+    </row>
+    <row r="258" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A258" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="B258" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="C258" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="34"/>
+      <c r="B259" s="34"/>
+      <c r="C259" s="34"/>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="25"/>
+      <c r="B260" s="25"/>
+      <c r="C260" s="25"/>
+    </row>
+    <row r="261" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A261" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="B261" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="C261" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="29"/>
+      <c r="B262" s="29"/>
+      <c r="C262" s="29"/>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="30"/>
+      <c r="B263" s="30"/>
+      <c r="C263" s="30"/>
+    </row>
+    <row r="264" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A264" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="B264" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="C264" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="34"/>
+      <c r="B265" s="34"/>
+      <c r="C265" s="34"/>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="25"/>
+      <c r="B266" s="25"/>
+      <c r="C266" s="25"/>
+    </row>
+    <row r="267" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A267" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B267" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="C267" s="28">
+        <v>1131124.74</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="29"/>
+      <c r="B268" s="29"/>
+      <c r="C268" s="29"/>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="30"/>
+      <c r="B269" s="30"/>
+      <c r="C269" s="30"/>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B270" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="C270" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="34"/>
+      <c r="B271" s="34"/>
+      <c r="C271" s="34"/>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="25"/>
+      <c r="B272" s="25"/>
+      <c r="C272" s="25"/>
+    </row>
+    <row r="273" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A273" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="B273" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="C273" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="29"/>
+      <c r="B274" s="29"/>
+      <c r="C274" s="29"/>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="30"/>
+      <c r="B275" s="30"/>
+      <c r="C275" s="30"/>
+    </row>
+    <row r="276" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A276" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="B276" s="32" t="s">
+        <v>250</v>
+      </c>
+      <c r="C276" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="34"/>
+      <c r="B277" s="34"/>
+      <c r="C277" s="34"/>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="25"/>
+      <c r="B278" s="25"/>
+      <c r="C278" s="25"/>
+    </row>
+    <row r="279" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A279" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B279" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C279" s="28">
+        <v>2459264.77</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="29"/>
+      <c r="B280" s="29"/>
+      <c r="C280" s="29"/>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="30"/>
+      <c r="B281" s="30"/>
+      <c r="C281" s="30"/>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="B282" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="C282" s="33">
+        <v>279805.15999999997</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="34"/>
+      <c r="B283" s="34"/>
+      <c r="C283" s="34"/>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="25"/>
+      <c r="B284" s="25"/>
+      <c r="C284" s="25"/>
+    </row>
+    <row r="285" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A285" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B285" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="C285" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="29"/>
+      <c r="B286" s="29"/>
+      <c r="C286" s="29"/>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="30"/>
+      <c r="B287" s="30"/>
+      <c r="C287" s="30"/>
+    </row>
+    <row r="288" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A288" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B288" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="C288" s="33">
+        <v>1705937.66</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="34"/>
+      <c r="B289" s="34"/>
+      <c r="C289" s="34"/>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="25"/>
+      <c r="B290" s="25"/>
+      <c r="C290" s="25"/>
+    </row>
+    <row r="291" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A291" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="B291" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="C291" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="29"/>
+      <c r="B292" s="29"/>
+      <c r="C292" s="29"/>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="30"/>
+      <c r="B293" s="30"/>
+      <c r="C293" s="30"/>
+    </row>
+    <row r="294" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A294" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="B294" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="C294" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="34"/>
+      <c r="B295" s="34"/>
+      <c r="C295" s="34"/>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="25"/>
+      <c r="B296" s="25"/>
+      <c r="C296" s="25"/>
+    </row>
+    <row r="297" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A297" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="B297" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C297" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="29"/>
+      <c r="B298" s="29"/>
+      <c r="C298" s="29"/>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="30"/>
+      <c r="B299" s="30"/>
+      <c r="C299" s="30"/>
+    </row>
+    <row r="300" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A300" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="B300" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="C300" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="34"/>
+      <c r="B301" s="34"/>
+      <c r="C301" s="34"/>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="25"/>
+      <c r="B302" s="25"/>
+      <c r="C302" s="25"/>
+    </row>
+    <row r="303" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A303" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B303" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C303" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="29"/>
+      <c r="B304" s="29"/>
+      <c r="C304" s="29"/>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="30"/>
+      <c r="B305" s="30"/>
+      <c r="C305" s="30"/>
+    </row>
+    <row r="306" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A306" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="B306" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="C306" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="34"/>
+      <c r="B307" s="34"/>
+      <c r="C307" s="34"/>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="25"/>
+      <c r="B308" s="25"/>
+      <c r="C308" s="25"/>
+    </row>
+    <row r="309" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A309" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="B309" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="C309" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="29"/>
+      <c r="B310" s="29"/>
+      <c r="C310" s="29"/>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="30"/>
+      <c r="B311" s="30"/>
+      <c r="C311" s="30"/>
+    </row>
+    <row r="312" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A312" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="B312" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="C312" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="34"/>
+      <c r="B313" s="34"/>
+      <c r="C313" s="34"/>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="25"/>
+      <c r="B314" s="25"/>
+      <c r="C314" s="25"/>
+    </row>
+    <row r="315" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A315" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="B315" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="C315" s="28">
+        <v>13381038.51</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="29"/>
+      <c r="B316" s="29"/>
+      <c r="C316" s="29"/>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="30"/>
+      <c r="B317" s="30"/>
+      <c r="C317" s="30"/>
+    </row>
+    <row r="318" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A318" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="B318" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="C318" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="34"/>
+      <c r="B319" s="34"/>
+      <c r="C319" s="34"/>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="25"/>
+      <c r="B320" s="25"/>
+      <c r="C320" s="25"/>
+    </row>
+    <row r="321" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A321" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="B321" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="C321" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="29"/>
+      <c r="B322" s="29"/>
+      <c r="C322" s="29"/>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="30"/>
+      <c r="B323" s="30"/>
+      <c r="C323" s="30"/>
+    </row>
+    <row r="324" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A324" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="B324" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="C324" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="34"/>
+      <c r="B325" s="34"/>
+      <c r="C325" s="34"/>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="25"/>
+      <c r="B326" s="25"/>
+      <c r="C326" s="25"/>
+    </row>
+    <row r="327" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A327" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B327" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="C327" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="29"/>
+      <c r="B328" s="29"/>
+      <c r="C328" s="29"/>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="30"/>
+      <c r="B329" s="30"/>
+      <c r="C329" s="30"/>
+    </row>
+    <row r="330" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A330" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="B330" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="C330" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="34"/>
+      <c r="B331" s="34"/>
+      <c r="C331" s="34"/>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="25"/>
+      <c r="B332" s="25"/>
+      <c r="C332" s="25"/>
+    </row>
+    <row r="333" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A333" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="B333" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="C333" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="29"/>
+      <c r="B334" s="29"/>
+      <c r="C334" s="29"/>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="30"/>
+      <c r="B335" s="30"/>
+      <c r="C335" s="30"/>
+    </row>
+    <row r="336" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A336" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B336" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="C336" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="34"/>
+      <c r="B337" s="34"/>
+      <c r="C337" s="34"/>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="25"/>
+      <c r="B338" s="25"/>
+      <c r="C338" s="25"/>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="B339" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C339" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="29"/>
+      <c r="B340" s="29"/>
+      <c r="C340" s="29"/>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="30"/>
+      <c r="B341" s="30"/>
+      <c r="C341" s="30"/>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="B342" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="C342" s="33">
+        <v>37306167.600000001</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" s="34"/>
+      <c r="B343" s="34"/>
+      <c r="C343" s="34"/>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="25"/>
+      <c r="B344" s="25"/>
+      <c r="C344" s="25"/>
+    </row>
+    <row r="345" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A345" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="B345" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="C345" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="29"/>
+      <c r="B346" s="29"/>
+      <c r="C346" s="29"/>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="30"/>
+      <c r="B347" s="30"/>
+      <c r="C347" s="30"/>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="B348" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="C348" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="34"/>
+      <c r="B349" s="34"/>
+      <c r="C349" s="34"/>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="25"/>
+      <c r="B350" s="25"/>
+      <c r="C350" s="25"/>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="B351" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="C351" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="29"/>
+      <c r="B352" s="29"/>
+      <c r="C352" s="29"/>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" s="36"/>
+      <c r="B353" s="36"/>
+      <c r="C353" s="36"/>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="B354" s="38" t="s">
+        <v>297</v>
+      </c>
+      <c r="C354" s="39">
+        <v>83661263.640000001</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" s="40"/>
+      <c r="B355" s="40"/>
+      <c r="C355" s="40"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/공사 데이터 입력 자동화/6월_매출손익현황.xlsx
+++ b/공사 데이터 입력 자동화/6월_매출손익현황.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\조성현\Documents\GitHub\yjs_Dashboard\공사 데이터 입력 자동화\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A52062E-D6AB-4677-B26D-1AD56D8D4452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5CCE54-50EA-401D-8A65-AAF0D7813DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="420" windowWidth="22620" windowHeight="14805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1320" yWindow="1290" windowWidth="22620" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6월 공정현황" sheetId="2" r:id="rId1"/>
-    <sheet name="6월 8일" sheetId="3" r:id="rId2"/>
-    <sheet name="6월 9일" sheetId="4" r:id="rId3"/>
-    <sheet name="6월 10일" sheetId="5" r:id="rId4"/>
-    <sheet name="6월 11일" sheetId="6" r:id="rId5"/>
-    <sheet name="6월 12일" sheetId="7" r:id="rId6"/>
+    <sheet name="6월 15일" sheetId="8" r:id="rId2"/>
+    <sheet name="6월 8일" sheetId="3" r:id="rId3"/>
+    <sheet name="6월 9일" sheetId="4" r:id="rId4"/>
+    <sheet name="6월 10일" sheetId="5" r:id="rId5"/>
+    <sheet name="6월 11일" sheetId="6" r:id="rId6"/>
+    <sheet name="6월 12일" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="305">
   <si>
     <t>JY25-256</t>
   </si>
@@ -2767,7 +2768,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2919,6 +2920,11 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -3047,7 +3053,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3182,6 +3188,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3682,11 +3691,11 @@
         <v>36994000</v>
       </c>
       <c r="E8" s="2">
-        <v>13381038.51</v>
+        <v>14955278.33</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
-        <v>0.36170834486673514</v>
+        <v>0.40426226766502676</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -4102,11 +4111,11 @@
         <v>7472000</v>
       </c>
       <c r="E28" s="2">
-        <v>4035280.68</v>
+        <v>7472742</v>
       </c>
       <c r="F28" s="3">
         <f>E28/D28</f>
-        <v>0.5400536241970022</v>
+        <v>1.0000993040685224</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
@@ -4178,11 +4187,11 @@
       </c>
       <c r="E32" s="6">
         <f>SUM(E4:E31)</f>
-        <v>74679856.610000014</v>
+        <v>79691557.75</v>
       </c>
       <c r="F32" s="7">
         <f>IF(D32&gt;0,E32/D32,"-")</f>
-        <v>0.17397753432731511</v>
+        <v>0.18565301747233548</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4364,11 +4373,11 @@
       </c>
       <c r="E48" s="12">
         <f>E32+E46</f>
-        <v>83661263.640000015</v>
+        <v>88672964.780000001</v>
       </c>
       <c r="F48" s="13">
         <f>E48/D48</f>
-        <v>0.19490102187536404</v>
+        <v>0.20657650502038438</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
@@ -4394,6 +4403,2509 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DF3E24-A858-4FF0-8BBB-75D3F5ECBECA}">
+  <dimension ref="A1:C355"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+    </row>
+    <row r="3" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+    </row>
+    <row r="6" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+    </row>
+    <row r="9" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+    </row>
+    <row r="15" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="28">
+        <v>203500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="35"/>
+      <c r="C18" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+    </row>
+    <row r="21" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+    </row>
+    <row r="24" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="34"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+    </row>
+    <row r="27" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+    </row>
+    <row r="30" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="34"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+    </row>
+    <row r="36" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="25"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+    </row>
+    <row r="39" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+    </row>
+    <row r="42" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="34"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="25"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+    </row>
+    <row r="45" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+    </row>
+    <row r="48" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="34"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="25"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+    </row>
+    <row r="51" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+    </row>
+    <row r="54" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="34"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="25"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25"/>
+    </row>
+    <row r="57" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C57" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="29"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+    </row>
+    <row r="60" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B60" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="C60" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="34"/>
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="25"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+    </row>
+    <row r="63" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" s="28">
+        <v>1575342.96</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="29"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="B66" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C66" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="34"/>
+      <c r="B67" s="34"/>
+      <c r="C67" s="34"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="25"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+    </row>
+    <row r="69" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="29"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
+    </row>
+    <row r="72" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="B72" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="C72" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="34"/>
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="25"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+    </row>
+    <row r="75" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C75" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="29"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="30"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="30"/>
+    </row>
+    <row r="78" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="C78" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="34"/>
+      <c r="B79" s="34"/>
+      <c r="C79" s="34"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="25"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+    </row>
+    <row r="81" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C81" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="29"/>
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="30"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
+    </row>
+    <row r="84" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C84" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="34"/>
+      <c r="B85" s="34"/>
+      <c r="C85" s="34"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="25"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+    </row>
+    <row r="87" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A87" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C87" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="29"/>
+      <c r="B88" s="29"/>
+      <c r="C88" s="29"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="30"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
+    </row>
+    <row r="90" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B90" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C90" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="34"/>
+      <c r="B91" s="34"/>
+      <c r="C91" s="34"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="25"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="25"/>
+    </row>
+    <row r="93" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A93" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B93" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C93" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="29"/>
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="30"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
+    </row>
+    <row r="96" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B96" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C96" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="34"/>
+      <c r="B97" s="34"/>
+      <c r="C97" s="34"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="25"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="25"/>
+    </row>
+    <row r="99" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A99" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B99" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="C99" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="29"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="29"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="30"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="30"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="B102" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C102" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="34"/>
+      <c r="B103" s="34"/>
+      <c r="C103" s="34"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="25"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="25"/>
+    </row>
+    <row r="105" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A105" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B105" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C105" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="29"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="29"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="30"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="30"/>
+    </row>
+    <row r="108" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A108" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B108" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="C108" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="34"/>
+      <c r="B109" s="34"/>
+      <c r="C109" s="34"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="25"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="25"/>
+    </row>
+    <row r="111" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A111" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B111" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C111" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="29"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="29"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="30"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="30"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="B114" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="C114" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="34"/>
+      <c r="B115" s="34"/>
+      <c r="C115" s="34"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="25"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="25"/>
+    </row>
+    <row r="117" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A117" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C117" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="29"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="29"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="30"/>
+    </row>
+    <row r="120" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A120" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B120" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C120" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="34"/>
+      <c r="B121" s="34"/>
+      <c r="C121" s="34"/>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="25"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="25"/>
+    </row>
+    <row r="123" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A123" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="B123" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="C123" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="29"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="29"/>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="30"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="30"/>
+    </row>
+    <row r="126" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A126" s="31" t="s">
+        <v>303</v>
+      </c>
+      <c r="B126" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="C126" s="33">
+        <v>7472742</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="34"/>
+      <c r="B127" s="34"/>
+      <c r="C127" s="34"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="25"/>
+      <c r="B128" s="25"/>
+      <c r="C128" s="25"/>
+    </row>
+    <row r="129" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="B129" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="C129" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="29"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="29"/>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="30"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="30"/>
+    </row>
+    <row r="132" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A132" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="B132" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="C132" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="34"/>
+      <c r="B133" s="34"/>
+      <c r="C133" s="34"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="25"/>
+      <c r="B134" s="25"/>
+      <c r="C134" s="25"/>
+    </row>
+    <row r="135" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A135" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="B135" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="C135" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="29"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="29"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="30"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="30"/>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="B138" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="C138" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="34"/>
+      <c r="B139" s="34"/>
+      <c r="C139" s="34"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="25"/>
+      <c r="B140" s="25"/>
+      <c r="C140" s="25"/>
+    </row>
+    <row r="141" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A141" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="B141" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="C141" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="29"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="29"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="30"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="30"/>
+    </row>
+    <row r="144" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A144" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B144" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="C144" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="34"/>
+      <c r="B145" s="34"/>
+      <c r="C145" s="34"/>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="25"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="25"/>
+    </row>
+    <row r="147" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A147" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="B147" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C147" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="29"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="29"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="30"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="30"/>
+    </row>
+    <row r="150" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A150" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="B150" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="C150" s="33">
+        <v>898035.92</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="34"/>
+      <c r="B151" s="34"/>
+      <c r="C151" s="34"/>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="25"/>
+      <c r="B152" s="25"/>
+      <c r="C152" s="25"/>
+    </row>
+    <row r="153" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A153" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="B153" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C153" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="29"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="29"/>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="30"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="30"/>
+    </row>
+    <row r="156" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A156" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="B156" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="C156" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="34"/>
+      <c r="B157" s="34"/>
+      <c r="C157" s="34"/>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="25"/>
+      <c r="B158" s="25"/>
+      <c r="C158" s="25"/>
+    </row>
+    <row r="159" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A159" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="B159" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C159" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="29"/>
+      <c r="B160" s="29"/>
+      <c r="C160" s="29"/>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="30"/>
+      <c r="B161" s="30"/>
+      <c r="C161" s="30"/>
+    </row>
+    <row r="162" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A162" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="B162" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="C162" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="34"/>
+      <c r="B163" s="34"/>
+      <c r="C163" s="34"/>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="25"/>
+      <c r="B164" s="25"/>
+      <c r="C164" s="25"/>
+    </row>
+    <row r="165" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A165" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="B165" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="C165" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="29"/>
+      <c r="B166" s="29"/>
+      <c r="C166" s="29"/>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="30"/>
+      <c r="B167" s="30"/>
+      <c r="C167" s="30"/>
+    </row>
+    <row r="168" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A168" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="B168" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="C168" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="34"/>
+      <c r="B169" s="34"/>
+      <c r="C169" s="34"/>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="25"/>
+      <c r="B170" s="25"/>
+      <c r="C170" s="25"/>
+    </row>
+    <row r="171" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A171" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="B171" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="C171" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="29"/>
+      <c r="B172" s="29"/>
+      <c r="C172" s="29"/>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="30"/>
+      <c r="B173" s="30"/>
+      <c r="C173" s="30"/>
+    </row>
+    <row r="174" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A174" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="B174" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C174" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="34"/>
+      <c r="B175" s="34"/>
+      <c r="C175" s="34"/>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="25"/>
+      <c r="B176" s="25"/>
+      <c r="C176" s="25"/>
+    </row>
+    <row r="177" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A177" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B177" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="C177" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
+      <c r="C178" s="29"/>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="30"/>
+      <c r="B179" s="30"/>
+      <c r="C179" s="30"/>
+    </row>
+    <row r="180" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A180" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B180" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C180" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="34"/>
+      <c r="B181" s="34"/>
+      <c r="C181" s="34"/>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="25"/>
+      <c r="B182" s="25"/>
+      <c r="C182" s="25"/>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="B183" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="C183" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="29"/>
+      <c r="B184" s="29"/>
+      <c r="C184" s="29"/>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="30"/>
+      <c r="B185" s="30"/>
+      <c r="C185" s="30"/>
+    </row>
+    <row r="186" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A186" s="31" t="s">
+        <v>200</v>
+      </c>
+      <c r="B186" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="C186" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="34"/>
+      <c r="B187" s="34"/>
+      <c r="C187" s="34"/>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="25"/>
+      <c r="B188" s="25"/>
+      <c r="C188" s="25"/>
+    </row>
+    <row r="189" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A189" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="B189" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="C189" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="29"/>
+      <c r="B190" s="29"/>
+      <c r="C190" s="29"/>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="30"/>
+      <c r="B191" s="30"/>
+      <c r="C191" s="30"/>
+    </row>
+    <row r="192" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A192" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="B192" s="32" t="s">
+        <v>205</v>
+      </c>
+      <c r="C192" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="34"/>
+      <c r="B193" s="34"/>
+      <c r="C193" s="34"/>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="25"/>
+      <c r="B194" s="25"/>
+      <c r="C194" s="25"/>
+    </row>
+    <row r="195" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A195" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="B195" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C195" s="28">
+        <v>405701.07</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="29"/>
+      <c r="B196" s="29"/>
+      <c r="C196" s="29"/>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="30"/>
+      <c r="B197" s="30"/>
+      <c r="C197" s="30"/>
+    </row>
+    <row r="198" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A198" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="B198" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C198" s="33">
+        <v>9903715.0800000001</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="34"/>
+      <c r="B199" s="34"/>
+      <c r="C199" s="34"/>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="25"/>
+      <c r="B200" s="25"/>
+      <c r="C200" s="25"/>
+    </row>
+    <row r="201" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A201" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B201" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="C201" s="28">
+        <v>1629647.99</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="29"/>
+      <c r="B202" s="29"/>
+      <c r="C202" s="29"/>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="30"/>
+      <c r="B203" s="30"/>
+      <c r="C203" s="30"/>
+    </row>
+    <row r="204" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A204" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="B204" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="C204" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="34"/>
+      <c r="B205" s="34"/>
+      <c r="C205" s="34"/>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="25"/>
+      <c r="B206" s="25"/>
+      <c r="C206" s="25"/>
+    </row>
+    <row r="207" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A207" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="B207" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="C207" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="29"/>
+      <c r="B208" s="29"/>
+      <c r="C208" s="29"/>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="30"/>
+      <c r="B209" s="30"/>
+      <c r="C209" s="30"/>
+    </row>
+    <row r="210" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A210" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="B210" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="C210" s="33">
+        <v>6256891.4800000004</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="34"/>
+      <c r="B211" s="34"/>
+      <c r="C211" s="34"/>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="25"/>
+      <c r="B212" s="25"/>
+      <c r="C212" s="25"/>
+    </row>
+    <row r="213" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A213" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="B213" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="C213" s="28">
+        <v>17285.71</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="29"/>
+      <c r="B214" s="29"/>
+      <c r="C214" s="29"/>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="30"/>
+      <c r="B215" s="30"/>
+      <c r="C215" s="30"/>
+    </row>
+    <row r="216" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A216" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="B216" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="C216" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="34"/>
+      <c r="B217" s="34"/>
+      <c r="C217" s="34"/>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="25"/>
+      <c r="B218" s="25"/>
+      <c r="C218" s="25"/>
+    </row>
+    <row r="219" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A219" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="B219" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="C219" s="28">
+        <v>203883.27</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="29"/>
+      <c r="B220" s="29"/>
+      <c r="C220" s="29"/>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="30"/>
+      <c r="B221" s="30"/>
+      <c r="C221" s="30"/>
+    </row>
+    <row r="222" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A222" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B222" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="C222" s="33">
+        <v>925466.57</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="34"/>
+      <c r="B223" s="34"/>
+      <c r="C223" s="34"/>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="25"/>
+      <c r="B224" s="25"/>
+      <c r="C224" s="25"/>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="B225" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C225" s="28">
+        <v>507687.92</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="29"/>
+      <c r="B226" s="29"/>
+      <c r="C226" s="29"/>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="30"/>
+      <c r="B227" s="30"/>
+      <c r="C227" s="30"/>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="B228" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="C228" s="33">
+        <v>835486.55</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="34"/>
+      <c r="B229" s="34"/>
+      <c r="C229" s="34"/>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="25"/>
+      <c r="B230" s="25"/>
+      <c r="C230" s="25"/>
+    </row>
+    <row r="231" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A231" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="B231" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="C231" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="29"/>
+      <c r="B232" s="29"/>
+      <c r="C232" s="29"/>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="30"/>
+      <c r="B233" s="30"/>
+      <c r="C233" s="30"/>
+    </row>
+    <row r="234" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A234" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="B234" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="C234" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="34"/>
+      <c r="B235" s="34"/>
+      <c r="C235" s="34"/>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="25"/>
+      <c r="B236" s="25"/>
+      <c r="C236" s="25"/>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="B237" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C237" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="29"/>
+      <c r="B238" s="29"/>
+      <c r="C238" s="29"/>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="30"/>
+      <c r="B239" s="30"/>
+      <c r="C239" s="30"/>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="31" t="s">
+        <v>227</v>
+      </c>
+      <c r="B240" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="C240" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="34"/>
+      <c r="B241" s="34"/>
+      <c r="C241" s="34"/>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="25"/>
+      <c r="B242" s="25"/>
+      <c r="C242" s="25"/>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="B243" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="C243" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="29"/>
+      <c r="B244" s="29"/>
+      <c r="C244" s="29"/>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="30"/>
+      <c r="B245" s="30"/>
+      <c r="C245" s="30"/>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="B246" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="C246" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="34"/>
+      <c r="B247" s="34"/>
+      <c r="C247" s="34"/>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="25"/>
+      <c r="B248" s="25"/>
+      <c r="C248" s="25"/>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="B249" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="C249" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="29"/>
+      <c r="B250" s="29"/>
+      <c r="C250" s="29"/>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="30"/>
+      <c r="B251" s="30"/>
+      <c r="C251" s="30"/>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="B252" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="C252" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="34"/>
+      <c r="B253" s="34"/>
+      <c r="C253" s="34"/>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="25"/>
+      <c r="B254" s="25"/>
+      <c r="C254" s="25"/>
+    </row>
+    <row r="255" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A255" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="B255" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="C255" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="29"/>
+      <c r="B256" s="29"/>
+      <c r="C256" s="29"/>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="30"/>
+      <c r="B257" s="30"/>
+      <c r="C257" s="30"/>
+    </row>
+    <row r="258" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A258" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="B258" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="C258" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="34"/>
+      <c r="B259" s="34"/>
+      <c r="C259" s="34"/>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="25"/>
+      <c r="B260" s="25"/>
+      <c r="C260" s="25"/>
+    </row>
+    <row r="261" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A261" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="B261" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="C261" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="29"/>
+      <c r="B262" s="29"/>
+      <c r="C262" s="29"/>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="30"/>
+      <c r="B263" s="30"/>
+      <c r="C263" s="30"/>
+    </row>
+    <row r="264" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A264" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="B264" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="C264" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="34"/>
+      <c r="B265" s="34"/>
+      <c r="C265" s="34"/>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="25"/>
+      <c r="B266" s="25"/>
+      <c r="C266" s="25"/>
+    </row>
+    <row r="267" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A267" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B267" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="C267" s="28">
+        <v>1131124.74</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="29"/>
+      <c r="B268" s="29"/>
+      <c r="C268" s="29"/>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="30"/>
+      <c r="B269" s="30"/>
+      <c r="C269" s="30"/>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B270" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="C270" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="34"/>
+      <c r="B271" s="34"/>
+      <c r="C271" s="34"/>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="25"/>
+      <c r="B272" s="25"/>
+      <c r="C272" s="25"/>
+    </row>
+    <row r="273" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A273" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="B273" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="C273" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="29"/>
+      <c r="B274" s="29"/>
+      <c r="C274" s="29"/>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="30"/>
+      <c r="B275" s="30"/>
+      <c r="C275" s="30"/>
+    </row>
+    <row r="276" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A276" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="B276" s="32" t="s">
+        <v>250</v>
+      </c>
+      <c r="C276" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="34"/>
+      <c r="B277" s="34"/>
+      <c r="C277" s="34"/>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="25"/>
+      <c r="B278" s="25"/>
+      <c r="C278" s="25"/>
+    </row>
+    <row r="279" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A279" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B279" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C279" s="28">
+        <v>2459264.77</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="29"/>
+      <c r="B280" s="29"/>
+      <c r="C280" s="29"/>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="30"/>
+      <c r="B281" s="30"/>
+      <c r="C281" s="30"/>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="B282" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="C282" s="33">
+        <v>279805.15999999997</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="34"/>
+      <c r="B283" s="34"/>
+      <c r="C283" s="34"/>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="25"/>
+      <c r="B284" s="25"/>
+      <c r="C284" s="25"/>
+    </row>
+    <row r="285" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A285" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B285" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="C285" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="29"/>
+      <c r="B286" s="29"/>
+      <c r="C286" s="29"/>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="30"/>
+      <c r="B287" s="30"/>
+      <c r="C287" s="30"/>
+    </row>
+    <row r="288" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A288" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B288" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="C288" s="33">
+        <v>1705937.66</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="34"/>
+      <c r="B289" s="34"/>
+      <c r="C289" s="34"/>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="25"/>
+      <c r="B290" s="25"/>
+      <c r="C290" s="25"/>
+    </row>
+    <row r="291" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A291" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="B291" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="C291" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="29"/>
+      <c r="B292" s="29"/>
+      <c r="C292" s="29"/>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="30"/>
+      <c r="B293" s="30"/>
+      <c r="C293" s="30"/>
+    </row>
+    <row r="294" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A294" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="B294" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="C294" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="34"/>
+      <c r="B295" s="34"/>
+      <c r="C295" s="34"/>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="25"/>
+      <c r="B296" s="25"/>
+      <c r="C296" s="25"/>
+    </row>
+    <row r="297" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A297" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="B297" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C297" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="29"/>
+      <c r="B298" s="29"/>
+      <c r="C298" s="29"/>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="30"/>
+      <c r="B299" s="30"/>
+      <c r="C299" s="30"/>
+    </row>
+    <row r="300" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A300" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="B300" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="C300" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="34"/>
+      <c r="B301" s="34"/>
+      <c r="C301" s="34"/>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="25"/>
+      <c r="B302" s="25"/>
+      <c r="C302" s="25"/>
+    </row>
+    <row r="303" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A303" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B303" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C303" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="29"/>
+      <c r="B304" s="29"/>
+      <c r="C304" s="29"/>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="30"/>
+      <c r="B305" s="30"/>
+      <c r="C305" s="30"/>
+    </row>
+    <row r="306" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A306" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="B306" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="C306" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="34"/>
+      <c r="B307" s="34"/>
+      <c r="C307" s="34"/>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="25"/>
+      <c r="B308" s="25"/>
+      <c r="C308" s="25"/>
+    </row>
+    <row r="309" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A309" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="B309" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="C309" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="29"/>
+      <c r="B310" s="29"/>
+      <c r="C310" s="29"/>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="30"/>
+      <c r="B311" s="30"/>
+      <c r="C311" s="30"/>
+    </row>
+    <row r="312" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A312" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="B312" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="C312" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="34"/>
+      <c r="B313" s="34"/>
+      <c r="C313" s="34"/>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="25"/>
+      <c r="B314" s="25"/>
+      <c r="C314" s="25"/>
+    </row>
+    <row r="315" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A315" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="B315" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="C315" s="28">
+        <v>14955278.33</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="29"/>
+      <c r="B316" s="29"/>
+      <c r="C316" s="29"/>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="30"/>
+      <c r="B317" s="30"/>
+      <c r="C317" s="30"/>
+    </row>
+    <row r="318" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A318" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="B318" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="C318" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="34"/>
+      <c r="B319" s="34"/>
+      <c r="C319" s="34"/>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="25"/>
+      <c r="B320" s="25"/>
+      <c r="C320" s="25"/>
+    </row>
+    <row r="321" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A321" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="B321" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="C321" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="29"/>
+      <c r="B322" s="29"/>
+      <c r="C322" s="29"/>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="30"/>
+      <c r="B323" s="30"/>
+      <c r="C323" s="30"/>
+    </row>
+    <row r="324" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A324" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="B324" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="C324" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="34"/>
+      <c r="B325" s="34"/>
+      <c r="C325" s="34"/>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="25"/>
+      <c r="B326" s="25"/>
+      <c r="C326" s="25"/>
+    </row>
+    <row r="327" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A327" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B327" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="C327" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="29"/>
+      <c r="B328" s="29"/>
+      <c r="C328" s="29"/>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="30"/>
+      <c r="B329" s="30"/>
+      <c r="C329" s="30"/>
+    </row>
+    <row r="330" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A330" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="B330" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="C330" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="34"/>
+      <c r="B331" s="34"/>
+      <c r="C331" s="34"/>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="25"/>
+      <c r="B332" s="25"/>
+      <c r="C332" s="25"/>
+    </row>
+    <row r="333" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A333" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="B333" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="C333" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="29"/>
+      <c r="B334" s="29"/>
+      <c r="C334" s="29"/>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="30"/>
+      <c r="B335" s="30"/>
+      <c r="C335" s="30"/>
+    </row>
+    <row r="336" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A336" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B336" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="C336" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="34"/>
+      <c r="B337" s="34"/>
+      <c r="C337" s="34"/>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="25"/>
+      <c r="B338" s="25"/>
+      <c r="C338" s="25"/>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="B339" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C339" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="29"/>
+      <c r="B340" s="29"/>
+      <c r="C340" s="29"/>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="30"/>
+      <c r="B341" s="30"/>
+      <c r="C341" s="30"/>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="B342" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="C342" s="33">
+        <v>37306167.600000001</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" s="34"/>
+      <c r="B343" s="34"/>
+      <c r="C343" s="34"/>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="25"/>
+      <c r="B344" s="25"/>
+      <c r="C344" s="25"/>
+    </row>
+    <row r="345" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A345" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="B345" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="C345" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="29"/>
+      <c r="B346" s="29"/>
+      <c r="C346" s="29"/>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="30"/>
+      <c r="B347" s="30"/>
+      <c r="C347" s="30"/>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="B348" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="C348" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="34"/>
+      <c r="B349" s="34"/>
+      <c r="C349" s="34"/>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="25"/>
+      <c r="B350" s="25"/>
+      <c r="C350" s="25"/>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="B351" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="C351" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="29"/>
+      <c r="B352" s="29"/>
+      <c r="C352" s="29"/>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" s="36"/>
+      <c r="B353" s="36"/>
+      <c r="C353" s="36"/>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="B354" s="38" t="s">
+        <v>297</v>
+      </c>
+      <c r="C354" s="39">
+        <v>88672964.780000001</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" s="40"/>
+      <c r="B355" s="40"/>
+      <c r="C355" s="40"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14538598-A375-43C3-B69D-90DF5275F387}">
   <dimension ref="A1:C343"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6812,7 +9324,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA02A4D7-2E10-440F-B03E-5357A26588F6}">
   <dimension ref="A1:C346"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9252,7 +11764,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE5DBBE-FC44-4248-8D66-BE79894FA05F}">
   <dimension ref="A1:C346"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11692,7 +14204,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC5C1D8-3950-4A39-9E0E-EB4AB1040608}">
   <dimension ref="A1:C352"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14174,7 +16686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A83B120-DF0E-482F-A671-B91FA1F387E8}">
   <dimension ref="A1:C355"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/공사 데이터 입력 자동화/6월_매출손익현황.xlsx
+++ b/공사 데이터 입력 자동화/6월_매출손익현황.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\조성현\Documents\GitHub\yjs_Dashboard\공사 데이터 입력 자동화\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5CCE54-50EA-401D-8A65-AAF0D7813DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563C8F8C-FA1F-4294-A60C-1AA9D0B9F46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="1290" windowWidth="22620" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29745" yWindow="180" windowWidth="22620" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6월 공정현황" sheetId="2" r:id="rId1"/>
-    <sheet name="6월 15일" sheetId="8" r:id="rId2"/>
-    <sheet name="6월 8일" sheetId="3" r:id="rId3"/>
-    <sheet name="6월 9일" sheetId="4" r:id="rId4"/>
-    <sheet name="6월 10일" sheetId="5" r:id="rId5"/>
-    <sheet name="6월 11일" sheetId="6" r:id="rId6"/>
-    <sheet name="6월 12일" sheetId="7" r:id="rId7"/>
+    <sheet name="6월 17일" sheetId="9" r:id="rId2"/>
+    <sheet name="6월 15일" sheetId="8" r:id="rId3"/>
+    <sheet name="6월 8일" sheetId="3" r:id="rId4"/>
+    <sheet name="6월 9일" sheetId="4" r:id="rId5"/>
+    <sheet name="6월 10일" sheetId="5" r:id="rId6"/>
+    <sheet name="6월 11일" sheetId="6" r:id="rId7"/>
+    <sheet name="6월 12일" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="315">
   <si>
     <t>JY25-256</t>
   </si>
@@ -2758,6 +2759,36 @@
   </si>
   <si>
     <t>안양동 413-1 (주)대영플러스 일반용(갑)저압 120Kw 신설 외 1</t>
+  </si>
+  <si>
+    <t>CG26-002</t>
+  </si>
+  <si>
+    <t>배전선로 복구공사(SW043~TR043-2)</t>
+  </si>
+  <si>
+    <t>CG26-003</t>
+  </si>
+  <si>
+    <t>일직동 511-2(신아에이앤아이 저압 30KW) 전기공급공사</t>
+  </si>
+  <si>
+    <t>CG26-004</t>
+  </si>
+  <si>
+    <t>소하동 1389-2(광명시청 저압 3W) 수급지점변경 전기공급공사</t>
+  </si>
+  <si>
+    <t>JG26-020</t>
+  </si>
+  <si>
+    <t>하안동 서정우 일반용(을) 고압A 10KW 계약단위분할</t>
+  </si>
+  <si>
+    <t>JG26-023</t>
+  </si>
+  <si>
+    <t>(지중)하안동 샤브향기(주) 일반용(갑)저압 88kW 증설</t>
   </si>
 </sst>
 </file>
@@ -3053,7 +3084,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3180,6 +3211,9 @@
     <xf numFmtId="49" fontId="21" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3189,8 +3223,8 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3559,22 +3593,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42"/>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="A1" s="43"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
     </row>
     <row r="3" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3796,11 +3830,11 @@
         <v>45588000</v>
       </c>
       <c r="E13" s="2">
-        <v>0</v>
+        <v>42421920.210000001</v>
       </c>
       <c r="F13" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.93055014938141623</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -4069,11 +4103,11 @@
         <v>1137000</v>
       </c>
       <c r="E26" s="2">
-        <v>0</v>
+        <v>1137419.8</v>
       </c>
       <c r="F26" s="3">
         <f>E26/D26</f>
-        <v>0</v>
+        <v>1.0003692172383465</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
@@ -4090,11 +4124,11 @@
         <v>395000</v>
       </c>
       <c r="E27" s="2">
-        <v>0</v>
+        <v>395368.8</v>
       </c>
       <c r="F27" s="3">
         <f>E27/D27</f>
-        <v>0</v>
+        <v>1.0009336708860759</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
@@ -4187,22 +4221,22 @@
       </c>
       <c r="E32" s="6">
         <f>SUM(E4:E31)</f>
-        <v>79691557.75</v>
+        <v>123646266.55999994</v>
       </c>
       <c r="F32" s="7">
         <f>IF(D32&gt;0,E32/D32,"-")</f>
-        <v>0.18565301747233548</v>
+        <v>0.28805187317414083</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="44" t="s">
+      <c r="A34" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="44"/>
-      <c r="C34" s="44"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
     </row>
     <row r="35" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -4232,7 +4266,7 @@
         <v>80</v>
       </c>
       <c r="E36" s="2">
-        <v>279805.15999999997</v>
+        <v>235497.52</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
@@ -4306,13 +4340,29 @@
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E42" s="2"/>
+      <c r="A42" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="C42" t="s">
+        <v>312</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2560247.4</v>
+      </c>
       <c r="F42" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E43" s="2"/>
+      <c r="A43" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="C43" t="s">
+        <v>314</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1407068.44</v>
+      </c>
       <c r="F43" t="s">
         <v>14</v>
       </c>
@@ -4344,7 +4394,7 @@
       </c>
       <c r="E46" s="10">
         <f>SUM(E36:E45)</f>
-        <v>8981407.0300000012</v>
+        <v>12904415.23</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>14</v>
@@ -4373,11 +4423,11 @@
       </c>
       <c r="E48" s="12">
         <f>E32+E46</f>
-        <v>88672964.780000001</v>
+        <v>136550681.78999993</v>
       </c>
       <c r="F48" s="13">
         <f>E48/D48</f>
-        <v>0.20657650502038438</v>
+        <v>0.31811457609784494</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
@@ -4403,6 +4453,2614 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E8162BD-A1EE-4E02-A97F-F6E2F6307379}">
+  <dimension ref="A1:C370"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+    </row>
+    <row r="3" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+    </row>
+    <row r="6" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="C6" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+    </row>
+    <row r="9" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="C9" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
+        <v>309</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="C12" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+    </row>
+    <row r="15" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+    </row>
+    <row r="18" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+    </row>
+    <row r="21" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+    </row>
+    <row r="24" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="33">
+        <v>203500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="34"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="46"/>
+      <c r="C27" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+    </row>
+    <row r="30" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="34"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+    </row>
+    <row r="33" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+    </row>
+    <row r="36" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="25"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+    </row>
+    <row r="39" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="34"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="25"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+    </row>
+    <row r="45" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+    </row>
+    <row r="48" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="34"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="25"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+    </row>
+    <row r="51" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+    </row>
+    <row r="54" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="34"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="25"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25"/>
+    </row>
+    <row r="57" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="29"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+    </row>
+    <row r="60" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C60" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="34"/>
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="25"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+    </row>
+    <row r="63" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C63" s="28">
+        <v>2560247.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="29"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+    </row>
+    <row r="66" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="31" t="s">
+        <v>313</v>
+      </c>
+      <c r="B66" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="C66" s="33">
+        <v>1407068.44</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="34"/>
+      <c r="B67" s="34"/>
+      <c r="C67" s="34"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="25"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+    </row>
+    <row r="69" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="C69" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="29"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
+    </row>
+    <row r="72" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="B72" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="C72" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="34"/>
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="25"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+    </row>
+    <row r="75" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C75" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="29"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="30"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="30"/>
+    </row>
+    <row r="78" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C78" s="33">
+        <v>1575342.96</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="34"/>
+      <c r="B79" s="34"/>
+      <c r="C79" s="34"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="25"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C81" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="29"/>
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="30"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
+    </row>
+    <row r="84" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="B84" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C84" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="34"/>
+      <c r="B85" s="34"/>
+      <c r="C85" s="34"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="25"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+    </row>
+    <row r="87" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A87" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C87" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="29"/>
+      <c r="B88" s="29"/>
+      <c r="C88" s="29"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="30"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
+    </row>
+    <row r="90" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="B90" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="C90" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="34"/>
+      <c r="B91" s="34"/>
+      <c r="C91" s="34"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="25"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="25"/>
+    </row>
+    <row r="93" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A93" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="B93" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="C93" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="29"/>
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="30"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
+    </row>
+    <row r="96" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B96" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C96" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="34"/>
+      <c r="B97" s="34"/>
+      <c r="C97" s="34"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="25"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="25"/>
+    </row>
+    <row r="99" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A99" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B99" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C99" s="28">
+        <v>395368.8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="29"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="29"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="30"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="30"/>
+    </row>
+    <row r="102" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A102" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B102" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="C102" s="33">
+        <v>1137419.8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="34"/>
+      <c r="B103" s="34"/>
+      <c r="C103" s="34"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="25"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="25"/>
+    </row>
+    <row r="105" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A105" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="B105" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C105" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="29"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="29"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="30"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="30"/>
+    </row>
+    <row r="108" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A108" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="B108" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="C108" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="34"/>
+      <c r="B109" s="34"/>
+      <c r="C109" s="34"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="25"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="25"/>
+    </row>
+    <row r="111" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A111" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B111" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C111" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="29"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="29"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="30"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="30"/>
+    </row>
+    <row r="114" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A114" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="B114" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="C114" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="34"/>
+      <c r="B115" s="34"/>
+      <c r="C115" s="34"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="25"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="25"/>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C117" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="29"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="29"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="30"/>
+    </row>
+    <row r="120" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A120" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="B120" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="C120" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="34"/>
+      <c r="B121" s="34"/>
+      <c r="C121" s="34"/>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="25"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="25"/>
+    </row>
+    <row r="123" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A123" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B123" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C123" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="29"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="29"/>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="30"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="30"/>
+    </row>
+    <row r="126" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A126" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="B126" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="C126" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="34"/>
+      <c r="B127" s="34"/>
+      <c r="C127" s="34"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="25"/>
+      <c r="B128" s="25"/>
+      <c r="C128" s="25"/>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="B129" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C129" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="29"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="29"/>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="30"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="30"/>
+    </row>
+    <row r="132" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A132" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="B132" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="C132" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="34"/>
+      <c r="B133" s="34"/>
+      <c r="C133" s="34"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="25"/>
+      <c r="B134" s="25"/>
+      <c r="C134" s="25"/>
+    </row>
+    <row r="135" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A135" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B135" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C135" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="29"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="29"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="30"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="30"/>
+    </row>
+    <row r="138" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A138" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="B138" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="C138" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="34"/>
+      <c r="B139" s="34"/>
+      <c r="C139" s="34"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="25"/>
+      <c r="B140" s="25"/>
+      <c r="C140" s="25"/>
+    </row>
+    <row r="141" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A141" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="B141" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="C141" s="28">
+        <v>7472742</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="29"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="29"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="30"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="30"/>
+    </row>
+    <row r="144" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A144" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B144" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="C144" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="34"/>
+      <c r="B145" s="34"/>
+      <c r="C145" s="34"/>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="25"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="25"/>
+    </row>
+    <row r="147" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A147" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="B147" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C147" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="29"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="29"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="30"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="30"/>
+    </row>
+    <row r="150" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A150" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="B150" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="C150" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="34"/>
+      <c r="B151" s="34"/>
+      <c r="C151" s="34"/>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="25"/>
+      <c r="B152" s="25"/>
+      <c r="C152" s="25"/>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="B153" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="C153" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="29"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="29"/>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="30"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="30"/>
+    </row>
+    <row r="156" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A156" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="B156" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C156" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="34"/>
+      <c r="B157" s="34"/>
+      <c r="C157" s="34"/>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="25"/>
+      <c r="B158" s="25"/>
+      <c r="C158" s="25"/>
+    </row>
+    <row r="159" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A159" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="B159" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="C159" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="29"/>
+      <c r="B160" s="29"/>
+      <c r="C160" s="29"/>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="30"/>
+      <c r="B161" s="30"/>
+      <c r="C161" s="30"/>
+    </row>
+    <row r="162" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A162" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B162" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C162" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="34"/>
+      <c r="B163" s="34"/>
+      <c r="C163" s="34"/>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="25"/>
+      <c r="B164" s="25"/>
+      <c r="C164" s="25"/>
+    </row>
+    <row r="165" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A165" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="B165" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C165" s="28">
+        <v>898035.92</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="29"/>
+      <c r="B166" s="29"/>
+      <c r="C166" s="29"/>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="30"/>
+      <c r="B167" s="30"/>
+      <c r="C167" s="30"/>
+    </row>
+    <row r="168" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A168" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B168" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="C168" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="34"/>
+      <c r="B169" s="34"/>
+      <c r="C169" s="34"/>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="25"/>
+      <c r="B170" s="25"/>
+      <c r="C170" s="25"/>
+    </row>
+    <row r="171" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A171" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="B171" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C171" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="29"/>
+      <c r="B172" s="29"/>
+      <c r="C172" s="29"/>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="30"/>
+      <c r="B173" s="30"/>
+      <c r="C173" s="30"/>
+    </row>
+    <row r="174" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A174" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="B174" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C174" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="34"/>
+      <c r="B175" s="34"/>
+      <c r="C175" s="34"/>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="25"/>
+      <c r="B176" s="25"/>
+      <c r="C176" s="25"/>
+    </row>
+    <row r="177" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A177" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="B177" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="C177" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
+      <c r="C178" s="29"/>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="30"/>
+      <c r="B179" s="30"/>
+      <c r="C179" s="30"/>
+    </row>
+    <row r="180" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A180" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="B180" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="C180" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="34"/>
+      <c r="B181" s="34"/>
+      <c r="C181" s="34"/>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="25"/>
+      <c r="B182" s="25"/>
+      <c r="C182" s="25"/>
+    </row>
+    <row r="183" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A183" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="B183" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="C183" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="29"/>
+      <c r="B184" s="29"/>
+      <c r="C184" s="29"/>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="30"/>
+      <c r="B185" s="30"/>
+      <c r="C185" s="30"/>
+    </row>
+    <row r="186" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A186" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="B186" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="C186" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="34"/>
+      <c r="B187" s="34"/>
+      <c r="C187" s="34"/>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="25"/>
+      <c r="B188" s="25"/>
+      <c r="C188" s="25"/>
+    </row>
+    <row r="189" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A189" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="B189" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C189" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="29"/>
+      <c r="B190" s="29"/>
+      <c r="C190" s="29"/>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="30"/>
+      <c r="B191" s="30"/>
+      <c r="C191" s="30"/>
+    </row>
+    <row r="192" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A192" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="B192" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C192" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="34"/>
+      <c r="B193" s="34"/>
+      <c r="C193" s="34"/>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="25"/>
+      <c r="B194" s="25"/>
+      <c r="C194" s="25"/>
+    </row>
+    <row r="195" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A195" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="B195" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C195" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="29"/>
+      <c r="B196" s="29"/>
+      <c r="C196" s="29"/>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="30"/>
+      <c r="B197" s="30"/>
+      <c r="C197" s="30"/>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="B198" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C198" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="34"/>
+      <c r="B199" s="34"/>
+      <c r="C199" s="34"/>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="25"/>
+      <c r="B200" s="25"/>
+      <c r="C200" s="25"/>
+    </row>
+    <row r="201" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A201" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="B201" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C201" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="29"/>
+      <c r="B202" s="29"/>
+      <c r="C202" s="29"/>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="30"/>
+      <c r="B203" s="30"/>
+      <c r="C203" s="30"/>
+    </row>
+    <row r="204" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A204" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="B204" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="C204" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="34"/>
+      <c r="B205" s="34"/>
+      <c r="C205" s="34"/>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="25"/>
+      <c r="B206" s="25"/>
+      <c r="C206" s="25"/>
+    </row>
+    <row r="207" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A207" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="B207" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="C207" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="29"/>
+      <c r="B208" s="29"/>
+      <c r="C208" s="29"/>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="30"/>
+      <c r="B209" s="30"/>
+      <c r="C209" s="30"/>
+    </row>
+    <row r="210" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A210" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="B210" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C210" s="33">
+        <v>405701.07</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="34"/>
+      <c r="B211" s="34"/>
+      <c r="C211" s="34"/>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="25"/>
+      <c r="B212" s="25"/>
+      <c r="C212" s="25"/>
+    </row>
+    <row r="213" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A213" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="B213" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C213" s="28">
+        <v>9903715.0800000001</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="29"/>
+      <c r="B214" s="29"/>
+      <c r="C214" s="29"/>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="30"/>
+      <c r="B215" s="30"/>
+      <c r="C215" s="30"/>
+    </row>
+    <row r="216" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A216" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B216" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="C216" s="33">
+        <v>1629647.99</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="34"/>
+      <c r="B217" s="34"/>
+      <c r="C217" s="34"/>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="25"/>
+      <c r="B218" s="25"/>
+      <c r="C218" s="25"/>
+    </row>
+    <row r="219" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A219" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="B219" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="C219" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="29"/>
+      <c r="B220" s="29"/>
+      <c r="C220" s="29"/>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="30"/>
+      <c r="B221" s="30"/>
+      <c r="C221" s="30"/>
+    </row>
+    <row r="222" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A222" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="B222" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="C222" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="34"/>
+      <c r="B223" s="34"/>
+      <c r="C223" s="34"/>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="25"/>
+      <c r="B224" s="25"/>
+      <c r="C224" s="25"/>
+    </row>
+    <row r="225" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A225" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B225" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="C225" s="28">
+        <v>6256891.4800000004</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="29"/>
+      <c r="B226" s="29"/>
+      <c r="C226" s="29"/>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="30"/>
+      <c r="B227" s="30"/>
+      <c r="C227" s="30"/>
+    </row>
+    <row r="228" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A228" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="B228" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="C228" s="33">
+        <v>17285.71</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="34"/>
+      <c r="B229" s="34"/>
+      <c r="C229" s="34"/>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="25"/>
+      <c r="B230" s="25"/>
+      <c r="C230" s="25"/>
+    </row>
+    <row r="231" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A231" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="B231" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="C231" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="29"/>
+      <c r="B232" s="29"/>
+      <c r="C232" s="29"/>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="30"/>
+      <c r="B233" s="30"/>
+      <c r="C233" s="30"/>
+    </row>
+    <row r="234" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A234" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="B234" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="C234" s="33">
+        <v>203883.27</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="34"/>
+      <c r="B235" s="34"/>
+      <c r="C235" s="34"/>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="25"/>
+      <c r="B236" s="25"/>
+      <c r="C236" s="25"/>
+    </row>
+    <row r="237" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A237" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B237" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="C237" s="28">
+        <v>925466.57</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="29"/>
+      <c r="B238" s="29"/>
+      <c r="C238" s="29"/>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="30"/>
+      <c r="B239" s="30"/>
+      <c r="C239" s="30"/>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="B240" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="C240" s="33">
+        <v>507687.92</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="34"/>
+      <c r="B241" s="34"/>
+      <c r="C241" s="34"/>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="25"/>
+      <c r="B242" s="25"/>
+      <c r="C242" s="25"/>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="B243" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C243" s="28">
+        <v>835486.55</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="29"/>
+      <c r="B244" s="29"/>
+      <c r="C244" s="29"/>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="30"/>
+      <c r="B245" s="30"/>
+      <c r="C245" s="30"/>
+    </row>
+    <row r="246" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A246" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="B246" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="C246" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="34"/>
+      <c r="B247" s="34"/>
+      <c r="C247" s="34"/>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="25"/>
+      <c r="B248" s="25"/>
+      <c r="C248" s="25"/>
+    </row>
+    <row r="249" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A249" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="B249" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C249" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="29"/>
+      <c r="B250" s="29"/>
+      <c r="C250" s="29"/>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="30"/>
+      <c r="B251" s="30"/>
+      <c r="C251" s="30"/>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="B252" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="C252" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="34"/>
+      <c r="B253" s="34"/>
+      <c r="C253" s="34"/>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="25"/>
+      <c r="B254" s="25"/>
+      <c r="C254" s="25"/>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="B255" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="C255" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="29"/>
+      <c r="B256" s="29"/>
+      <c r="C256" s="29"/>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="30"/>
+      <c r="B257" s="30"/>
+      <c r="C257" s="30"/>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="31" t="s">
+        <v>229</v>
+      </c>
+      <c r="B258" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="C258" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="34"/>
+      <c r="B259" s="34"/>
+      <c r="C259" s="34"/>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="25"/>
+      <c r="B260" s="25"/>
+      <c r="C260" s="25"/>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="B261" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="C261" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="29"/>
+      <c r="B262" s="29"/>
+      <c r="C262" s="29"/>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="30"/>
+      <c r="B263" s="30"/>
+      <c r="C263" s="30"/>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="B264" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="C264" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="34"/>
+      <c r="B265" s="34"/>
+      <c r="C265" s="34"/>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="25"/>
+      <c r="B266" s="25"/>
+      <c r="C266" s="25"/>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="B267" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C267" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="29"/>
+      <c r="B268" s="29"/>
+      <c r="C268" s="29"/>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="30"/>
+      <c r="B269" s="30"/>
+      <c r="C269" s="30"/>
+    </row>
+    <row r="270" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A270" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="B270" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="C270" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="34"/>
+      <c r="B271" s="34"/>
+      <c r="C271" s="34"/>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="25"/>
+      <c r="B272" s="25"/>
+      <c r="C272" s="25"/>
+    </row>
+    <row r="273" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A273" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="B273" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="C273" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="29"/>
+      <c r="B274" s="29"/>
+      <c r="C274" s="29"/>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="30"/>
+      <c r="B275" s="30"/>
+      <c r="C275" s="30"/>
+    </row>
+    <row r="276" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A276" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="B276" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="C276" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="34"/>
+      <c r="B277" s="34"/>
+      <c r="C277" s="34"/>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="25"/>
+      <c r="B278" s="25"/>
+      <c r="C278" s="25"/>
+    </row>
+    <row r="279" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A279" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="B279" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="C279" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="29"/>
+      <c r="B280" s="29"/>
+      <c r="C280" s="29"/>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="30"/>
+      <c r="B281" s="30"/>
+      <c r="C281" s="30"/>
+    </row>
+    <row r="282" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A282" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B282" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="C282" s="33">
+        <v>1131124.74</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="34"/>
+      <c r="B283" s="34"/>
+      <c r="C283" s="34"/>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="25"/>
+      <c r="B284" s="25"/>
+      <c r="C284" s="25"/>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B285" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="C285" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="29"/>
+      <c r="B286" s="29"/>
+      <c r="C286" s="29"/>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="30"/>
+      <c r="B287" s="30"/>
+      <c r="C287" s="30"/>
+    </row>
+    <row r="288" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A288" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="B288" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="C288" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="34"/>
+      <c r="B289" s="34"/>
+      <c r="C289" s="34"/>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="25"/>
+      <c r="B290" s="25"/>
+      <c r="C290" s="25"/>
+    </row>
+    <row r="291" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A291" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B291" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="C291" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="29"/>
+      <c r="B292" s="29"/>
+      <c r="C292" s="29"/>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="30"/>
+      <c r="B293" s="30"/>
+      <c r="C293" s="30"/>
+    </row>
+    <row r="294" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A294" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B294" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="C294" s="33">
+        <v>2459264.77</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="34"/>
+      <c r="B295" s="34"/>
+      <c r="C295" s="34"/>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="25"/>
+      <c r="B296" s="25"/>
+      <c r="C296" s="25"/>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="B297" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="C297" s="28">
+        <v>235497.52</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="29"/>
+      <c r="B298" s="29"/>
+      <c r="C298" s="29"/>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="30"/>
+      <c r="B299" s="30"/>
+      <c r="C299" s="30"/>
+    </row>
+    <row r="300" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A300" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="B300" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="C300" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="34"/>
+      <c r="B301" s="34"/>
+      <c r="C301" s="34"/>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="25"/>
+      <c r="B302" s="25"/>
+      <c r="C302" s="25"/>
+    </row>
+    <row r="303" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A303" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B303" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="C303" s="28">
+        <v>1705937.66</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="29"/>
+      <c r="B304" s="29"/>
+      <c r="C304" s="29"/>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="30"/>
+      <c r="B305" s="30"/>
+      <c r="C305" s="30"/>
+    </row>
+    <row r="306" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A306" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="B306" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="C306" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="34"/>
+      <c r="B307" s="34"/>
+      <c r="C307" s="34"/>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="25"/>
+      <c r="B308" s="25"/>
+      <c r="C308" s="25"/>
+    </row>
+    <row r="309" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A309" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B309" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="C309" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="29"/>
+      <c r="B310" s="29"/>
+      <c r="C310" s="29"/>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="30"/>
+      <c r="B311" s="30"/>
+      <c r="C311" s="30"/>
+    </row>
+    <row r="312" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A312" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="B312" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="C312" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="34"/>
+      <c r="B313" s="34"/>
+      <c r="C313" s="34"/>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="25"/>
+      <c r="B314" s="25"/>
+      <c r="C314" s="25"/>
+    </row>
+    <row r="315" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A315" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B315" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C315" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="29"/>
+      <c r="B316" s="29"/>
+      <c r="C316" s="29"/>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="30"/>
+      <c r="B317" s="30"/>
+      <c r="C317" s="30"/>
+    </row>
+    <row r="318" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A318" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B318" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="C318" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="34"/>
+      <c r="B319" s="34"/>
+      <c r="C319" s="34"/>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="25"/>
+      <c r="B320" s="25"/>
+      <c r="C320" s="25"/>
+    </row>
+    <row r="321" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A321" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="B321" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C321" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="29"/>
+      <c r="B322" s="29"/>
+      <c r="C322" s="29"/>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="30"/>
+      <c r="B323" s="30"/>
+      <c r="C323" s="30"/>
+    </row>
+    <row r="324" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A324" s="31" t="s">
+        <v>268</v>
+      </c>
+      <c r="B324" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="C324" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="34"/>
+      <c r="B325" s="34"/>
+      <c r="C325" s="34"/>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="25"/>
+      <c r="B326" s="25"/>
+      <c r="C326" s="25"/>
+    </row>
+    <row r="327" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A327" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="B327" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="C327" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="29"/>
+      <c r="B328" s="29"/>
+      <c r="C328" s="29"/>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="30"/>
+      <c r="B329" s="30"/>
+      <c r="C329" s="30"/>
+    </row>
+    <row r="330" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A330" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="B330" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="C330" s="33">
+        <v>14955278.33</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="34"/>
+      <c r="B331" s="34"/>
+      <c r="C331" s="34"/>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="25"/>
+      <c r="B332" s="25"/>
+      <c r="C332" s="25"/>
+    </row>
+    <row r="333" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A333" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="B333" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="C333" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="29"/>
+      <c r="B334" s="29"/>
+      <c r="C334" s="29"/>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="30"/>
+      <c r="B335" s="30"/>
+      <c r="C335" s="30"/>
+    </row>
+    <row r="336" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A336" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="B336" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="C336" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="34"/>
+      <c r="B337" s="34"/>
+      <c r="C337" s="34"/>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="25"/>
+      <c r="B338" s="25"/>
+      <c r="C338" s="25"/>
+    </row>
+    <row r="339" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A339" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="B339" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="C339" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="29"/>
+      <c r="B340" s="29"/>
+      <c r="C340" s="29"/>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="30"/>
+      <c r="B341" s="30"/>
+      <c r="C341" s="30"/>
+    </row>
+    <row r="342" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A342" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="B342" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="C342" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" s="34"/>
+      <c r="B343" s="34"/>
+      <c r="C343" s="34"/>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="25"/>
+      <c r="B344" s="25"/>
+      <c r="C344" s="25"/>
+    </row>
+    <row r="345" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A345" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="B345" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="C345" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="29"/>
+      <c r="B346" s="29"/>
+      <c r="C346" s="29"/>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="30"/>
+      <c r="B347" s="30"/>
+      <c r="C347" s="30"/>
+    </row>
+    <row r="348" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A348" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="B348" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="C348" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="34"/>
+      <c r="B349" s="34"/>
+      <c r="C349" s="34"/>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="25"/>
+      <c r="B350" s="25"/>
+      <c r="C350" s="25"/>
+    </row>
+    <row r="351" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A351" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B351" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="C351" s="28">
+        <v>42421920.210000001</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="29"/>
+      <c r="B352" s="29"/>
+      <c r="C352" s="29"/>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" s="30"/>
+      <c r="B353" s="30"/>
+      <c r="C353" s="30"/>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="B354" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C354" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" s="34"/>
+      <c r="B355" s="34"/>
+      <c r="C355" s="34"/>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" s="25"/>
+      <c r="B356" s="25"/>
+      <c r="C356" s="25"/>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B357" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="C357" s="28">
+        <v>37306167.600000001</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" s="29"/>
+      <c r="B358" s="29"/>
+      <c r="C358" s="29"/>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" s="30"/>
+      <c r="B359" s="30"/>
+      <c r="C359" s="30"/>
+    </row>
+    <row r="360" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A360" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="B360" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="C360" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" s="34"/>
+      <c r="B361" s="34"/>
+      <c r="C361" s="34"/>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" s="25"/>
+      <c r="B362" s="25"/>
+      <c r="C362" s="25"/>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="B363" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="C363" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" s="29"/>
+      <c r="B364" s="29"/>
+      <c r="C364" s="29"/>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" s="30"/>
+      <c r="B365" s="30"/>
+      <c r="C365" s="30"/>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="B366" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="C366" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" s="34"/>
+      <c r="B367" s="34"/>
+      <c r="C367" s="34"/>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" s="36"/>
+      <c r="B368" s="36"/>
+      <c r="C368" s="36"/>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="B369" s="38" t="s">
+        <v>297</v>
+      </c>
+      <c r="C369" s="39">
+        <v>136550681.78999999</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" s="40"/>
+      <c r="B370" s="40"/>
+      <c r="C370" s="40"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DF3E24-A858-4FF0-8BBB-75D3F5ECBECA}">
   <dimension ref="A1:C355"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4413,7 +7071,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="B1" s="24" t="s">
@@ -6905,7 +9563,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14538598-A375-43C3-B69D-90DF5275F387}">
   <dimension ref="A1:C343"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9324,7 +11982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA02A4D7-2E10-440F-B03E-5357A26588F6}">
   <dimension ref="A1:C346"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11764,7 +14422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE5DBBE-FC44-4248-8D66-BE79894FA05F}">
   <dimension ref="A1:C346"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14204,7 +16862,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC5C1D8-3950-4A39-9E0E-EB4AB1040608}">
   <dimension ref="A1:C352"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16686,7 +19344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A83B120-DF0E-482F-A671-B91FA1F387E8}">
   <dimension ref="A1:C355"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/공사 데이터 입력 자동화/6월_매출손익현황.xlsx
+++ b/공사 데이터 입력 자동화/6월_매출손익현황.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\조성현\Documents\GitHub\yjs_Dashboard\공사 데이터 입력 자동화\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563C8F8C-FA1F-4294-A60C-1AA9D0B9F46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5402EF-1CF0-43B9-8DD5-EDBD313EAF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29745" yWindow="180" windowWidth="22620" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4950" yWindow="0" windowWidth="22620" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6월 공정현황" sheetId="2" r:id="rId1"/>
-    <sheet name="6월 17일" sheetId="9" r:id="rId2"/>
-    <sheet name="6월 15일" sheetId="8" r:id="rId3"/>
-    <sheet name="6월 8일" sheetId="3" r:id="rId4"/>
-    <sheet name="6월 9일" sheetId="4" r:id="rId5"/>
-    <sheet name="6월 10일" sheetId="5" r:id="rId6"/>
-    <sheet name="6월 11일" sheetId="6" r:id="rId7"/>
-    <sheet name="6월 12일" sheetId="7" r:id="rId8"/>
+    <sheet name="6월 18일" sheetId="10" r:id="rId2"/>
+    <sheet name="6월 17일" sheetId="9" r:id="rId3"/>
+    <sheet name="6월 15일" sheetId="8" r:id="rId4"/>
+    <sheet name="6월 8일" sheetId="3" r:id="rId5"/>
+    <sheet name="6월 9일" sheetId="4" r:id="rId6"/>
+    <sheet name="6월 10일" sheetId="5" r:id="rId7"/>
+    <sheet name="6월 11일" sheetId="6" r:id="rId8"/>
+    <sheet name="6월 12일" sheetId="7" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="319">
   <si>
     <t>JY25-256</t>
   </si>
@@ -2789,6 +2790,18 @@
   </si>
   <si>
     <t>(지중)하안동 샤브향기(주) 일반용(갑)저압 88kW 증설</t>
+  </si>
+  <si>
+    <t>JG26-022</t>
+  </si>
+  <si>
+    <t>(지중)하안동 광명시청 일반용(갑)저압 300kw 신설(상용/임시)</t>
+  </si>
+  <si>
+    <t>JY25-254</t>
+  </si>
+  <si>
+    <t>초평동641-2 김명호 5kW 신설</t>
   </si>
 </sst>
 </file>
@@ -3214,6 +3227,9 @@
     <xf numFmtId="49" fontId="22" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3222,9 +3238,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3593,22 +3606,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43"/>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
+      <c r="A1" s="44"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
     </row>
     <row r="3" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3830,11 +3843,11 @@
         <v>45588000</v>
       </c>
       <c r="E13" s="2">
-        <v>42421920.210000001</v>
+        <v>45587735.149999999</v>
       </c>
       <c r="F13" s="3">
         <f t="shared" si="1"/>
-        <v>0.93055014938141623</v>
+        <v>0.99999419035711146</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -4188,11 +4201,11 @@
         <v>15102000</v>
       </c>
       <c r="E30" s="2">
-        <v>0</v>
+        <v>7549642.0899999999</v>
       </c>
       <c r="F30" s="3">
         <f>E30/D30</f>
-        <v>0</v>
+        <v>0.49991008409482185</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
@@ -4221,22 +4234,22 @@
       </c>
       <c r="E32" s="6">
         <f>SUM(E4:E31)</f>
-        <v>123646266.55999994</v>
+        <v>134361723.58999994</v>
       </c>
       <c r="F32" s="7">
         <f>IF(D32&gt;0,E32/D32,"-")</f>
-        <v>0.28805187317414083</v>
+        <v>0.31301508116482224</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="45" t="s">
+      <c r="A34" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
     </row>
     <row r="35" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -4368,7 +4381,15 @@
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E44" s="2"/>
+      <c r="A44" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="C44" t="s">
+        <v>318</v>
+      </c>
+      <c r="E44" s="2">
+        <v>2053383</v>
+      </c>
       <c r="F44" t="s">
         <v>14</v>
       </c>
@@ -4394,7 +4415,7 @@
       </c>
       <c r="E46" s="10">
         <f>SUM(E36:E45)</f>
-        <v>12904415.23</v>
+        <v>14957798.23</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>14</v>
@@ -4423,11 +4444,11 @@
       </c>
       <c r="E48" s="12">
         <f>E32+E46</f>
-        <v>136550681.78999993</v>
+        <v>149319521.81999993</v>
       </c>
       <c r="F48" s="13">
         <f>E48/D48</f>
-        <v>0.31811457609784494</v>
+        <v>0.34786143697146171</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
@@ -4453,6 +4474,2656 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA6CC55-FEF7-4098-9961-1CB408A9EC8E}">
+  <dimension ref="A1:C376"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+    </row>
+    <row r="3" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+    </row>
+    <row r="6" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="C6" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+    </row>
+    <row r="9" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="C9" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
+        <v>309</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="C12" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+    </row>
+    <row r="15" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+    </row>
+    <row r="18" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+    </row>
+    <row r="21" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+    </row>
+    <row r="24" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="33">
+        <v>203500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="34"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="43"/>
+      <c r="C27" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+    </row>
+    <row r="30" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="34"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+    </row>
+    <row r="33" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+    </row>
+    <row r="36" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="25"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+    </row>
+    <row r="39" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="34"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="25"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+    </row>
+    <row r="45" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+    </row>
+    <row r="48" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="34"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="25"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+    </row>
+    <row r="51" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+    </row>
+    <row r="54" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="34"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="25"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25"/>
+    </row>
+    <row r="57" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="29"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+    </row>
+    <row r="60" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C60" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="34"/>
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="25"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+    </row>
+    <row r="63" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C63" s="28">
+        <v>2560247.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="29"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+    </row>
+    <row r="66" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="31" t="s">
+        <v>315</v>
+      </c>
+      <c r="B66" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="C66" s="33">
+        <v>7549642.0899999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="34"/>
+      <c r="B67" s="34"/>
+      <c r="C67" s="34"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="25"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+    </row>
+    <row r="69" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C69" s="28">
+        <v>1407068.44</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="29"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
+    </row>
+    <row r="72" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B72" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="C72" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="34"/>
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="25"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+    </row>
+    <row r="75" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C75" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="29"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="30"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="30"/>
+    </row>
+    <row r="78" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="C78" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="34"/>
+      <c r="B79" s="34"/>
+      <c r="C79" s="34"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="25"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+    </row>
+    <row r="81" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="C81" s="28">
+        <v>1575342.96</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="29"/>
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="30"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="B84" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C84" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="34"/>
+      <c r="B85" s="34"/>
+      <c r="C85" s="34"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="25"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+    </row>
+    <row r="87" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A87" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C87" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="29"/>
+      <c r="B88" s="29"/>
+      <c r="C88" s="29"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="30"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
+    </row>
+    <row r="90" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="B90" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="C90" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="34"/>
+      <c r="B91" s="34"/>
+      <c r="C91" s="34"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="25"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="25"/>
+    </row>
+    <row r="93" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A93" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B93" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C93" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="29"/>
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="30"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
+    </row>
+    <row r="96" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="B96" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="C96" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="34"/>
+      <c r="B97" s="34"/>
+      <c r="C97" s="34"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="25"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="25"/>
+    </row>
+    <row r="99" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A99" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B99" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C99" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="29"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="29"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="30"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="30"/>
+    </row>
+    <row r="102" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A102" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B102" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C102" s="33">
+        <v>395368.8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="34"/>
+      <c r="B103" s="34"/>
+      <c r="C103" s="34"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="25"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="25"/>
+    </row>
+    <row r="105" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A105" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B105" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C105" s="28">
+        <v>1137419.8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="29"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="29"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="30"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="30"/>
+    </row>
+    <row r="108" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A108" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B108" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C108" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="34"/>
+      <c r="B109" s="34"/>
+      <c r="C109" s="34"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="25"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="25"/>
+    </row>
+    <row r="111" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A111" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B111" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C111" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="29"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="29"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="30"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="30"/>
+    </row>
+    <row r="114" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A114" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B114" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C114" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="34"/>
+      <c r="B115" s="34"/>
+      <c r="C115" s="34"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="25"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="25"/>
+    </row>
+    <row r="117" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A117" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="C117" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="29"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="29"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="30"/>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="B120" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C120" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="34"/>
+      <c r="B121" s="34"/>
+      <c r="C121" s="34"/>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="25"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="25"/>
+    </row>
+    <row r="123" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A123" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B123" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C123" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="29"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="29"/>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="30"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="30"/>
+    </row>
+    <row r="126" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A126" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B126" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="C126" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="34"/>
+      <c r="B127" s="34"/>
+      <c r="C127" s="34"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="25"/>
+      <c r="B128" s="25"/>
+      <c r="C128" s="25"/>
+    </row>
+    <row r="129" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B129" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C129" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="29"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="29"/>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="30"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="30"/>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="B132" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="C132" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="34"/>
+      <c r="B133" s="34"/>
+      <c r="C133" s="34"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="25"/>
+      <c r="B134" s="25"/>
+      <c r="C134" s="25"/>
+    </row>
+    <row r="135" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A135" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="B135" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C135" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="29"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="29"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="30"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="30"/>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="31" t="s">
+        <v>317</v>
+      </c>
+      <c r="B138" s="32" t="s">
+        <v>318</v>
+      </c>
+      <c r="C138" s="33">
+        <v>2053383</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="34"/>
+      <c r="B139" s="34"/>
+      <c r="C139" s="34"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="25"/>
+      <c r="B140" s="25"/>
+      <c r="C140" s="25"/>
+    </row>
+    <row r="141" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A141" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B141" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C141" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="29"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="29"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="30"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="30"/>
+    </row>
+    <row r="144" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A144" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="B144" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="C144" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="34"/>
+      <c r="B145" s="34"/>
+      <c r="C145" s="34"/>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="25"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="25"/>
+    </row>
+    <row r="147" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A147" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="B147" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="C147" s="28">
+        <v>7472742</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="29"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="29"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="30"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="30"/>
+    </row>
+    <row r="150" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A150" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B150" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="C150" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="34"/>
+      <c r="B151" s="34"/>
+      <c r="C151" s="34"/>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="25"/>
+      <c r="B152" s="25"/>
+      <c r="C152" s="25"/>
+    </row>
+    <row r="153" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A153" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="B153" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C153" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="29"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="29"/>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="30"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="30"/>
+    </row>
+    <row r="156" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A156" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="B156" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="C156" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="34"/>
+      <c r="B157" s="34"/>
+      <c r="C157" s="34"/>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="25"/>
+      <c r="B158" s="25"/>
+      <c r="C158" s="25"/>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="B159" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="C159" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="29"/>
+      <c r="B160" s="29"/>
+      <c r="C160" s="29"/>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="30"/>
+      <c r="B161" s="30"/>
+      <c r="C161" s="30"/>
+    </row>
+    <row r="162" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A162" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="B162" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C162" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="34"/>
+      <c r="B163" s="34"/>
+      <c r="C163" s="34"/>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="25"/>
+      <c r="B164" s="25"/>
+      <c r="C164" s="25"/>
+    </row>
+    <row r="165" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A165" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="B165" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="C165" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="29"/>
+      <c r="B166" s="29"/>
+      <c r="C166" s="29"/>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="30"/>
+      <c r="B167" s="30"/>
+      <c r="C167" s="30"/>
+    </row>
+    <row r="168" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A168" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B168" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C168" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="34"/>
+      <c r="B169" s="34"/>
+      <c r="C169" s="34"/>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="25"/>
+      <c r="B170" s="25"/>
+      <c r="C170" s="25"/>
+    </row>
+    <row r="171" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A171" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="B171" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C171" s="28">
+        <v>898035.92</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="29"/>
+      <c r="B172" s="29"/>
+      <c r="C172" s="29"/>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="30"/>
+      <c r="B173" s="30"/>
+      <c r="C173" s="30"/>
+    </row>
+    <row r="174" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A174" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B174" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="C174" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="34"/>
+      <c r="B175" s="34"/>
+      <c r="C175" s="34"/>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="25"/>
+      <c r="B176" s="25"/>
+      <c r="C176" s="25"/>
+    </row>
+    <row r="177" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A177" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="B177" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C177" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
+      <c r="C178" s="29"/>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="30"/>
+      <c r="B179" s="30"/>
+      <c r="C179" s="30"/>
+    </row>
+    <row r="180" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A180" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="B180" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C180" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="34"/>
+      <c r="B181" s="34"/>
+      <c r="C181" s="34"/>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="25"/>
+      <c r="B182" s="25"/>
+      <c r="C182" s="25"/>
+    </row>
+    <row r="183" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A183" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="B183" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="C183" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="29"/>
+      <c r="B184" s="29"/>
+      <c r="C184" s="29"/>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="30"/>
+      <c r="B185" s="30"/>
+      <c r="C185" s="30"/>
+    </row>
+    <row r="186" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A186" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="B186" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="C186" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="34"/>
+      <c r="B187" s="34"/>
+      <c r="C187" s="34"/>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="25"/>
+      <c r="B188" s="25"/>
+      <c r="C188" s="25"/>
+    </row>
+    <row r="189" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A189" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="B189" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="C189" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="29"/>
+      <c r="B190" s="29"/>
+      <c r="C190" s="29"/>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="30"/>
+      <c r="B191" s="30"/>
+      <c r="C191" s="30"/>
+    </row>
+    <row r="192" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A192" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="B192" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="C192" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="34"/>
+      <c r="B193" s="34"/>
+      <c r="C193" s="34"/>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="25"/>
+      <c r="B194" s="25"/>
+      <c r="C194" s="25"/>
+    </row>
+    <row r="195" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A195" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="B195" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C195" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="29"/>
+      <c r="B196" s="29"/>
+      <c r="C196" s="29"/>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="30"/>
+      <c r="B197" s="30"/>
+      <c r="C197" s="30"/>
+    </row>
+    <row r="198" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A198" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="B198" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C198" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="34"/>
+      <c r="B199" s="34"/>
+      <c r="C199" s="34"/>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="25"/>
+      <c r="B200" s="25"/>
+      <c r="C200" s="25"/>
+    </row>
+    <row r="201" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A201" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="B201" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C201" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="29"/>
+      <c r="B202" s="29"/>
+      <c r="C202" s="29"/>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="30"/>
+      <c r="B203" s="30"/>
+      <c r="C203" s="30"/>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="B204" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C204" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="34"/>
+      <c r="B205" s="34"/>
+      <c r="C205" s="34"/>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="25"/>
+      <c r="B206" s="25"/>
+      <c r="C206" s="25"/>
+    </row>
+    <row r="207" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A207" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="B207" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C207" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="29"/>
+      <c r="B208" s="29"/>
+      <c r="C208" s="29"/>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="30"/>
+      <c r="B209" s="30"/>
+      <c r="C209" s="30"/>
+    </row>
+    <row r="210" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A210" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="B210" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="C210" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="34"/>
+      <c r="B211" s="34"/>
+      <c r="C211" s="34"/>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="25"/>
+      <c r="B212" s="25"/>
+      <c r="C212" s="25"/>
+    </row>
+    <row r="213" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A213" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="B213" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="C213" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="29"/>
+      <c r="B214" s="29"/>
+      <c r="C214" s="29"/>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="30"/>
+      <c r="B215" s="30"/>
+      <c r="C215" s="30"/>
+    </row>
+    <row r="216" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A216" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="B216" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C216" s="33">
+        <v>405701.07</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="34"/>
+      <c r="B217" s="34"/>
+      <c r="C217" s="34"/>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="25"/>
+      <c r="B218" s="25"/>
+      <c r="C218" s="25"/>
+    </row>
+    <row r="219" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A219" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="B219" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C219" s="28">
+        <v>9903715.0800000001</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="29"/>
+      <c r="B220" s="29"/>
+      <c r="C220" s="29"/>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="30"/>
+      <c r="B221" s="30"/>
+      <c r="C221" s="30"/>
+    </row>
+    <row r="222" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A222" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B222" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="C222" s="33">
+        <v>1629647.99</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="34"/>
+      <c r="B223" s="34"/>
+      <c r="C223" s="34"/>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="25"/>
+      <c r="B224" s="25"/>
+      <c r="C224" s="25"/>
+    </row>
+    <row r="225" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A225" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="B225" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="C225" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="29"/>
+      <c r="B226" s="29"/>
+      <c r="C226" s="29"/>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="30"/>
+      <c r="B227" s="30"/>
+      <c r="C227" s="30"/>
+    </row>
+    <row r="228" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A228" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="B228" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="C228" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="34"/>
+      <c r="B229" s="34"/>
+      <c r="C229" s="34"/>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="25"/>
+      <c r="B230" s="25"/>
+      <c r="C230" s="25"/>
+    </row>
+    <row r="231" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A231" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B231" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="C231" s="28">
+        <v>6256891.4800000004</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="29"/>
+      <c r="B232" s="29"/>
+      <c r="C232" s="29"/>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="30"/>
+      <c r="B233" s="30"/>
+      <c r="C233" s="30"/>
+    </row>
+    <row r="234" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A234" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="B234" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="C234" s="33">
+        <v>17285.71</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="34"/>
+      <c r="B235" s="34"/>
+      <c r="C235" s="34"/>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="25"/>
+      <c r="B236" s="25"/>
+      <c r="C236" s="25"/>
+    </row>
+    <row r="237" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A237" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="B237" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="C237" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="29"/>
+      <c r="B238" s="29"/>
+      <c r="C238" s="29"/>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="30"/>
+      <c r="B239" s="30"/>
+      <c r="C239" s="30"/>
+    </row>
+    <row r="240" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A240" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="B240" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="C240" s="33">
+        <v>203883.27</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="34"/>
+      <c r="B241" s="34"/>
+      <c r="C241" s="34"/>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="25"/>
+      <c r="B242" s="25"/>
+      <c r="C242" s="25"/>
+    </row>
+    <row r="243" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A243" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B243" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="C243" s="28">
+        <v>925466.57</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="29"/>
+      <c r="B244" s="29"/>
+      <c r="C244" s="29"/>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="30"/>
+      <c r="B245" s="30"/>
+      <c r="C245" s="30"/>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="B246" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="C246" s="33">
+        <v>507687.92</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="34"/>
+      <c r="B247" s="34"/>
+      <c r="C247" s="34"/>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="25"/>
+      <c r="B248" s="25"/>
+      <c r="C248" s="25"/>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="B249" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C249" s="28">
+        <v>835486.55</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="29"/>
+      <c r="B250" s="29"/>
+      <c r="C250" s="29"/>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="30"/>
+      <c r="B251" s="30"/>
+      <c r="C251" s="30"/>
+    </row>
+    <row r="252" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A252" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="B252" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="C252" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="34"/>
+      <c r="B253" s="34"/>
+      <c r="C253" s="34"/>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="25"/>
+      <c r="B254" s="25"/>
+      <c r="C254" s="25"/>
+    </row>
+    <row r="255" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A255" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="B255" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C255" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="29"/>
+      <c r="B256" s="29"/>
+      <c r="C256" s="29"/>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="30"/>
+      <c r="B257" s="30"/>
+      <c r="C257" s="30"/>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="B258" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="C258" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="34"/>
+      <c r="B259" s="34"/>
+      <c r="C259" s="34"/>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="25"/>
+      <c r="B260" s="25"/>
+      <c r="C260" s="25"/>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="B261" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="C261" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="29"/>
+      <c r="B262" s="29"/>
+      <c r="C262" s="29"/>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="30"/>
+      <c r="B263" s="30"/>
+      <c r="C263" s="30"/>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="31" t="s">
+        <v>229</v>
+      </c>
+      <c r="B264" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="C264" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="34"/>
+      <c r="B265" s="34"/>
+      <c r="C265" s="34"/>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="25"/>
+      <c r="B266" s="25"/>
+      <c r="C266" s="25"/>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="B267" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="C267" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="29"/>
+      <c r="B268" s="29"/>
+      <c r="C268" s="29"/>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="30"/>
+      <c r="B269" s="30"/>
+      <c r="C269" s="30"/>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="B270" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="C270" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="34"/>
+      <c r="B271" s="34"/>
+      <c r="C271" s="34"/>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="25"/>
+      <c r="B272" s="25"/>
+      <c r="C272" s="25"/>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="B273" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C273" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="29"/>
+      <c r="B274" s="29"/>
+      <c r="C274" s="29"/>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="30"/>
+      <c r="B275" s="30"/>
+      <c r="C275" s="30"/>
+    </row>
+    <row r="276" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A276" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="B276" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="C276" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="34"/>
+      <c r="B277" s="34"/>
+      <c r="C277" s="34"/>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="25"/>
+      <c r="B278" s="25"/>
+      <c r="C278" s="25"/>
+    </row>
+    <row r="279" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A279" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="B279" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="C279" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="29"/>
+      <c r="B280" s="29"/>
+      <c r="C280" s="29"/>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="30"/>
+      <c r="B281" s="30"/>
+      <c r="C281" s="30"/>
+    </row>
+    <row r="282" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A282" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="B282" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="C282" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="34"/>
+      <c r="B283" s="34"/>
+      <c r="C283" s="34"/>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="25"/>
+      <c r="B284" s="25"/>
+      <c r="C284" s="25"/>
+    </row>
+    <row r="285" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A285" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="B285" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="C285" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="29"/>
+      <c r="B286" s="29"/>
+      <c r="C286" s="29"/>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="30"/>
+      <c r="B287" s="30"/>
+      <c r="C287" s="30"/>
+    </row>
+    <row r="288" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A288" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B288" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="C288" s="33">
+        <v>1131124.74</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="34"/>
+      <c r="B289" s="34"/>
+      <c r="C289" s="34"/>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="25"/>
+      <c r="B290" s="25"/>
+      <c r="C290" s="25"/>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B291" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="C291" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="29"/>
+      <c r="B292" s="29"/>
+      <c r="C292" s="29"/>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="30"/>
+      <c r="B293" s="30"/>
+      <c r="C293" s="30"/>
+    </row>
+    <row r="294" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A294" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="B294" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="C294" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="34"/>
+      <c r="B295" s="34"/>
+      <c r="C295" s="34"/>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="25"/>
+      <c r="B296" s="25"/>
+      <c r="C296" s="25"/>
+    </row>
+    <row r="297" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A297" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B297" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="C297" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="29"/>
+      <c r="B298" s="29"/>
+      <c r="C298" s="29"/>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="30"/>
+      <c r="B299" s="30"/>
+      <c r="C299" s="30"/>
+    </row>
+    <row r="300" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A300" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B300" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="C300" s="33">
+        <v>2459264.77</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="34"/>
+      <c r="B301" s="34"/>
+      <c r="C301" s="34"/>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="25"/>
+      <c r="B302" s="25"/>
+      <c r="C302" s="25"/>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="B303" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="C303" s="28">
+        <v>235497.52</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="29"/>
+      <c r="B304" s="29"/>
+      <c r="C304" s="29"/>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="30"/>
+      <c r="B305" s="30"/>
+      <c r="C305" s="30"/>
+    </row>
+    <row r="306" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A306" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="B306" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="C306" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="34"/>
+      <c r="B307" s="34"/>
+      <c r="C307" s="34"/>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="25"/>
+      <c r="B308" s="25"/>
+      <c r="C308" s="25"/>
+    </row>
+    <row r="309" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A309" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B309" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="C309" s="28">
+        <v>1705937.66</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="29"/>
+      <c r="B310" s="29"/>
+      <c r="C310" s="29"/>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="30"/>
+      <c r="B311" s="30"/>
+      <c r="C311" s="30"/>
+    </row>
+    <row r="312" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A312" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="B312" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="C312" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="34"/>
+      <c r="B313" s="34"/>
+      <c r="C313" s="34"/>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="25"/>
+      <c r="B314" s="25"/>
+      <c r="C314" s="25"/>
+    </row>
+    <row r="315" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A315" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B315" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="C315" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="29"/>
+      <c r="B316" s="29"/>
+      <c r="C316" s="29"/>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="30"/>
+      <c r="B317" s="30"/>
+      <c r="C317" s="30"/>
+    </row>
+    <row r="318" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A318" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="B318" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="C318" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="34"/>
+      <c r="B319" s="34"/>
+      <c r="C319" s="34"/>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="25"/>
+      <c r="B320" s="25"/>
+      <c r="C320" s="25"/>
+    </row>
+    <row r="321" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A321" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B321" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C321" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="29"/>
+      <c r="B322" s="29"/>
+      <c r="C322" s="29"/>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="30"/>
+      <c r="B323" s="30"/>
+      <c r="C323" s="30"/>
+    </row>
+    <row r="324" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A324" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B324" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="C324" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="34"/>
+      <c r="B325" s="34"/>
+      <c r="C325" s="34"/>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="25"/>
+      <c r="B326" s="25"/>
+      <c r="C326" s="25"/>
+    </row>
+    <row r="327" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A327" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="B327" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C327" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="29"/>
+      <c r="B328" s="29"/>
+      <c r="C328" s="29"/>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="30"/>
+      <c r="B329" s="30"/>
+      <c r="C329" s="30"/>
+    </row>
+    <row r="330" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A330" s="31" t="s">
+        <v>268</v>
+      </c>
+      <c r="B330" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="C330" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="34"/>
+      <c r="B331" s="34"/>
+      <c r="C331" s="34"/>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="25"/>
+      <c r="B332" s="25"/>
+      <c r="C332" s="25"/>
+    </row>
+    <row r="333" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A333" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="B333" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="C333" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="29"/>
+      <c r="B334" s="29"/>
+      <c r="C334" s="29"/>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="30"/>
+      <c r="B335" s="30"/>
+      <c r="C335" s="30"/>
+    </row>
+    <row r="336" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A336" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="B336" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="C336" s="33">
+        <v>14955278.33</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="34"/>
+      <c r="B337" s="34"/>
+      <c r="C337" s="34"/>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="25"/>
+      <c r="B338" s="25"/>
+      <c r="C338" s="25"/>
+    </row>
+    <row r="339" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A339" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="B339" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="C339" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="29"/>
+      <c r="B340" s="29"/>
+      <c r="C340" s="29"/>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="30"/>
+      <c r="B341" s="30"/>
+      <c r="C341" s="30"/>
+    </row>
+    <row r="342" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A342" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="B342" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="C342" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" s="34"/>
+      <c r="B343" s="34"/>
+      <c r="C343" s="34"/>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="25"/>
+      <c r="B344" s="25"/>
+      <c r="C344" s="25"/>
+    </row>
+    <row r="345" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A345" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="B345" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="C345" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="29"/>
+      <c r="B346" s="29"/>
+      <c r="C346" s="29"/>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="30"/>
+      <c r="B347" s="30"/>
+      <c r="C347" s="30"/>
+    </row>
+    <row r="348" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A348" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="B348" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="C348" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="34"/>
+      <c r="B349" s="34"/>
+      <c r="C349" s="34"/>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="25"/>
+      <c r="B350" s="25"/>
+      <c r="C350" s="25"/>
+    </row>
+    <row r="351" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A351" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="B351" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="C351" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="29"/>
+      <c r="B352" s="29"/>
+      <c r="C352" s="29"/>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" s="30"/>
+      <c r="B353" s="30"/>
+      <c r="C353" s="30"/>
+    </row>
+    <row r="354" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A354" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="B354" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="C354" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" s="34"/>
+      <c r="B355" s="34"/>
+      <c r="C355" s="34"/>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" s="25"/>
+      <c r="B356" s="25"/>
+      <c r="C356" s="25"/>
+    </row>
+    <row r="357" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A357" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B357" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="C357" s="28">
+        <v>45587735.149999999</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" s="29"/>
+      <c r="B358" s="29"/>
+      <c r="C358" s="29"/>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" s="30"/>
+      <c r="B359" s="30"/>
+      <c r="C359" s="30"/>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="B360" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C360" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" s="34"/>
+      <c r="B361" s="34"/>
+      <c r="C361" s="34"/>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" s="25"/>
+      <c r="B362" s="25"/>
+      <c r="C362" s="25"/>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B363" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="C363" s="28">
+        <v>37306167.600000001</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" s="29"/>
+      <c r="B364" s="29"/>
+      <c r="C364" s="29"/>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" s="30"/>
+      <c r="B365" s="30"/>
+      <c r="C365" s="30"/>
+    </row>
+    <row r="366" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A366" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="B366" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="C366" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" s="34"/>
+      <c r="B367" s="34"/>
+      <c r="C367" s="34"/>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" s="25"/>
+      <c r="B368" s="25"/>
+      <c r="C368" s="25"/>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="B369" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="C369" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" s="29"/>
+      <c r="B370" s="29"/>
+      <c r="C370" s="29"/>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" s="30"/>
+      <c r="B371" s="30"/>
+      <c r="C371" s="30"/>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="B372" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="C372" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" s="34"/>
+      <c r="B373" s="34"/>
+      <c r="C373" s="34"/>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" s="36"/>
+      <c r="B374" s="36"/>
+      <c r="C374" s="36"/>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="B375" s="38" t="s">
+        <v>297</v>
+      </c>
+      <c r="C375" s="39">
+        <v>149319521.81999999</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" s="40"/>
+      <c r="B376" s="40"/>
+      <c r="C376" s="40"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E8162BD-A1EE-4E02-A97F-F6E2F6307379}">
   <dimension ref="A1:C370"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4650,7 +7321,7 @@
       <c r="A27" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B27" s="46"/>
+      <c r="B27" s="43"/>
       <c r="C27" s="28">
         <v>0</v>
       </c>
@@ -7060,7 +9731,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DF3E24-A858-4FF0-8BBB-75D3F5ECBECA}">
   <dimension ref="A1:C355"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9563,7 +12234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14538598-A375-43C3-B69D-90DF5275F387}">
   <dimension ref="A1:C343"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11982,7 +14653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA02A4D7-2E10-440F-B03E-5357A26588F6}">
   <dimension ref="A1:C346"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14422,7 +17093,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE5DBBE-FC44-4248-8D66-BE79894FA05F}">
   <dimension ref="A1:C346"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16862,7 +19533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC5C1D8-3950-4A39-9E0E-EB4AB1040608}">
   <dimension ref="A1:C352"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19344,7 +22015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A83B120-DF0E-482F-A671-B91FA1F387E8}">
   <dimension ref="A1:C355"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
